--- a/GearSage-client/pkgGear/data_raw/shimano_line_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_line_import.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:K60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,13 +431,16 @@
       <c r="J1" t="str">
         <v>updated_at</v>
       </c>
+      <c r="K1" t="str">
+        <v>description</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>SLN1000</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
         <v>Tanatoru 8</v>
@@ -462,14 +465,17 @@
       </c>
       <c r="J2" t="str">
         <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>SLN1001</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
         <v>Tanatoru 4 / 8 100m  连盘</v>
@@ -494,14 +500,17 @@
       </c>
       <c r="J3" t="str">
         <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>SLN1002</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
         <v>PITBULL G9</v>
@@ -526,14 +535,17 @@
       </c>
       <c r="J4" t="str">
         <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>SLN1003</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
         <v>OCEA PLUGGER NYLON LEADER</v>
@@ -558,14 +570,17 @@
       </c>
       <c r="J5" t="str">
         <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>SLN1004</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
         <v>PITBULL FLUORO LEADER</v>
@@ -590,14 +605,17 @@
       </c>
       <c r="J6" t="str">
         <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>SLN1005</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>1</v>
       </c>
       <c r="C7" t="str">
         <v>OCEA 17+</v>
@@ -622,14 +640,17 @@
       </c>
       <c r="J7" t="str">
         <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>SLN1006</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>1</v>
       </c>
       <c r="C8" t="str">
         <v>OCEA 8</v>
@@ -654,14 +675,17 @@
       </c>
       <c r="J8" t="str">
         <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>SLN1007</v>
       </c>
-      <c r="B9" t="str">
-        <v/>
+      <c r="B9">
+        <v>1</v>
       </c>
       <c r="C9" t="str">
         <v>OCEA JIGGER MX4</v>
@@ -686,14 +710,17 @@
       </c>
       <c r="J9" t="str">
         <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v>SLN1008</v>
       </c>
-      <c r="B10" t="str">
-        <v/>
+      <c r="B10">
+        <v>1</v>
       </c>
       <c r="C10" t="str">
         <v>KISU SPECIAL EX4</v>
@@ -718,14 +745,17 @@
       </c>
       <c r="J10" t="str">
         <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v>SLN1009</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
+      <c r="B11">
+        <v>1</v>
       </c>
       <c r="C11" t="str">
         <v>KISU SPECIAL G5</v>
@@ -750,14 +780,17 @@
       </c>
       <c r="J11" t="str">
         <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
         <v>SLN1010</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="B12">
+        <v>1</v>
       </c>
       <c r="C12" t="str">
         <v>OCEA EX 前导线</v>
@@ -782,14 +815,17 @@
       </c>
       <c r="J12" t="str">
         <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>SLN1011</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>1</v>
       </c>
       <c r="C13" t="str">
         <v>LIMITED PRO G5+ PE</v>
@@ -814,14 +850,17 @@
       </c>
       <c r="J13" t="str">
         <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
         <v>SLN1012</v>
       </c>
-      <c r="B14" t="str">
-        <v/>
+      <c r="B14">
+        <v>1</v>
       </c>
       <c r="C14" t="str">
         <v>PITBULL 12</v>
@@ -846,14 +885,17 @@
       </c>
       <c r="J14" t="str">
         <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v>SLN1013</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
+      <c r="B15">
+        <v>1</v>
       </c>
       <c r="C15" t="str">
         <v>HARDBULL 8+</v>
@@ -878,14 +920,17 @@
       </c>
       <c r="J15" t="str">
         <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v>SLN1014</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
+      <c r="B16">
+        <v>1</v>
       </c>
       <c r="C16" t="str">
         <v>GRAPPLER 8</v>
@@ -910,14 +955,17 @@
       </c>
       <c r="J16" t="str">
         <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
         <v>SLN1015</v>
       </c>
-      <c r="B17" t="str">
-        <v/>
+      <c r="B17">
+        <v>1</v>
       </c>
       <c r="C17" t="str">
         <v>KISU SPECIAL EX4 13m</v>
@@ -942,14 +990,17 @@
       </c>
       <c r="J17" t="str">
         <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v>SLN1016</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
+      <c r="B18">
+        <v>1</v>
       </c>
       <c r="C18" t="str">
         <v>Tanatoru 4</v>
@@ -974,14 +1025,17 @@
       </c>
       <c r="J18" t="str">
         <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v>SLN1017</v>
       </c>
-      <c r="B19" t="str">
-        <v/>
+      <c r="B19">
+        <v>1</v>
       </c>
       <c r="C19" t="str">
         <v>KAIKON</v>
@@ -1006,14 +1060,17 @@
       </c>
       <c r="J19" t="str">
         <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v>SLN1018</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
+      <c r="B20">
+        <v>1</v>
       </c>
       <c r="C20" t="str">
         <v>BULL'S EYE 远投</v>
@@ -1038,14 +1095,17 @@
       </c>
       <c r="J20" t="str">
         <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v>SLN1019</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>1</v>
       </c>
       <c r="C21" t="str">
         <v>OCEA JIGGER MASTER 前导线</v>
@@ -1070,14 +1130,17 @@
       </c>
       <c r="J21" t="str">
         <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v>SLN1020</v>
       </c>
-      <c r="B22" t="str">
-        <v/>
+      <c r="B22">
+        <v>1</v>
       </c>
       <c r="C22" t="str">
         <v>Sephia 8+</v>
@@ -1102,14 +1165,17 @@
       </c>
       <c r="J22" t="str">
         <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
         <v>SLN1021</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
+      <c r="B23">
+        <v>1</v>
       </c>
       <c r="C23" t="str">
         <v>PITBULL 8+</v>
@@ -1134,14 +1200,17 @@
       </c>
       <c r="J23" t="str">
         <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
         <v>SLN1022</v>
       </c>
-      <c r="B24" t="str">
-        <v/>
+      <c r="B24">
+        <v>1</v>
       </c>
       <c r="C24" t="str">
         <v>FUKASE 船</v>
@@ -1166,14 +1235,17 @@
       </c>
       <c r="J24" t="str">
         <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
         <v>SLN1023</v>
       </c>
-      <c r="B25" t="str">
-        <v/>
+      <c r="B25">
+        <v>1</v>
       </c>
       <c r="C25" t="str">
         <v>Sephia G5</v>
@@ -1198,14 +1270,17 @@
       </c>
       <c r="J25" t="str">
         <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v>SLN1024</v>
       </c>
-      <c r="B26" t="str">
-        <v/>
+      <c r="B26">
+        <v>1</v>
       </c>
       <c r="C26" t="str">
         <v>Sephia 8</v>
@@ -1230,14 +1305,17 @@
       </c>
       <c r="J26" t="str">
         <v/>
+      </c>
+      <c r="K26" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
         <v>SLN1025</v>
       </c>
-      <c r="B27" t="str">
-        <v/>
+      <c r="B27">
+        <v>1</v>
       </c>
       <c r="C27" t="str">
         <v>SPINPOWER EX4</v>
@@ -1262,14 +1340,17 @@
       </c>
       <c r="J27" t="str">
         <v/>
+      </c>
+      <c r="K27" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v>SLN1026</v>
       </c>
-      <c r="B28" t="str">
-        <v/>
+      <c r="B28">
+        <v>1</v>
       </c>
       <c r="C28" t="str">
         <v>GRAPPLER 4</v>
@@ -1294,14 +1375,17 @@
       </c>
       <c r="J28" t="str">
         <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v>SLN1027</v>
       </c>
-      <c r="B29" t="str">
-        <v/>
+      <c r="B29">
+        <v>1</v>
       </c>
       <c r="C29" t="str">
         <v>LAKEMASTER</v>
@@ -1326,14 +1410,17 @@
       </c>
       <c r="J29" t="str">
         <v/>
+      </c>
+      <c r="K29" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
         <v>SLN1028</v>
       </c>
-      <c r="B30" t="str">
-        <v/>
+      <c r="B30">
+        <v>1</v>
       </c>
       <c r="C30" t="str">
         <v>LIMITED PRO MASTER TOUGH-MUD</v>
@@ -1358,14 +1445,17 @@
       </c>
       <c r="J30" t="str">
         <v/>
+      </c>
+      <c r="K30" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v>SLN1029</v>
       </c>
-      <c r="B31" t="str">
-        <v/>
+      <c r="B31">
+        <v>1</v>
       </c>
       <c r="C31" t="str">
         <v>LIMITED PRO MASTER</v>
@@ -1390,14 +1480,17 @@
       </c>
       <c r="J31" t="str">
         <v/>
+      </c>
+      <c r="K31" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v>SLN1030</v>
       </c>
-      <c r="B32" t="str">
-        <v/>
+      <c r="B32">
+        <v>1</v>
       </c>
       <c r="C32" t="str">
         <v>BB-X HYPER-REPEL α 漂浮</v>
@@ -1422,14 +1515,17 @@
       </c>
       <c r="J32" t="str">
         <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v>SLN1031</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
+      <c r="B33">
+        <v>1</v>
       </c>
       <c r="C33" t="str">
         <v>BB-X PLASMA WHITE FLOAT</v>
@@ -1454,14 +1550,17 @@
       </c>
       <c r="J33" t="str">
         <v/>
+      </c>
+      <c r="K33" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
         <v>SLN1032</v>
       </c>
-      <c r="B34" t="str">
-        <v/>
+      <c r="B34">
+        <v>1</v>
       </c>
       <c r="C34" t="str">
         <v>PITBULL 4</v>
@@ -1486,14 +1585,17 @@
       </c>
       <c r="J34" t="str">
         <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
         <v>SLN1033</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
+      <c r="B35">
+        <v>1</v>
       </c>
       <c r="C35" t="str">
         <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮</v>
@@ -1518,14 +1620,17 @@
       </c>
       <c r="J35" t="str">
         <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v>SLN1034</v>
       </c>
-      <c r="B36" t="str">
-        <v/>
+      <c r="B36">
+        <v>1</v>
       </c>
       <c r="C36" t="str">
         <v>LIMITED PRO 矶 ZERO 悬停 150m</v>
@@ -1550,14 +1655,17 @@
       </c>
       <c r="J36" t="str">
         <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v>SLN1035</v>
       </c>
-      <c r="B37" t="str">
-        <v/>
+      <c r="B37">
+        <v>1</v>
       </c>
       <c r="C37" t="str">
         <v>BB-X PLASMA WHITE ZERO SUSPEND</v>
@@ -1582,14 +1690,17 @@
       </c>
       <c r="J37" t="str">
         <v/>
+      </c>
+      <c r="K37" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v>SLN1036</v>
       </c>
-      <c r="B38" t="str">
-        <v/>
+      <c r="B38">
+        <v>1</v>
       </c>
       <c r="C38" t="str">
         <v>MASTIFF FC 90m</v>
@@ -1614,14 +1725,17 @@
       </c>
       <c r="J38" t="str">
         <v/>
+      </c>
+      <c r="K38" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
         <v>SLN1037</v>
       </c>
-      <c r="B39" t="str">
-        <v/>
+      <c r="B39">
+        <v>1</v>
       </c>
       <c r="C39" t="str">
         <v>OCEA 前导线</v>
@@ -1646,14 +1760,17 @@
       </c>
       <c r="J39" t="str">
         <v/>
+      </c>
+      <c r="K39" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v>SLN1038</v>
       </c>
-      <c r="B40" t="str">
-        <v/>
+      <c r="B40">
+        <v>1</v>
       </c>
       <c r="C40" t="str">
         <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮</v>
@@ -1678,14 +1795,17 @@
       </c>
       <c r="J40" t="str">
         <v/>
+      </c>
+      <c r="K40" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v>SLN1039</v>
       </c>
-      <c r="B41" t="str">
-        <v/>
+      <c r="B41">
+        <v>1</v>
       </c>
       <c r="C41" t="str">
         <v>FIREBLOOD HYPER-REPEL α ZERO 悬停</v>
@@ -1710,14 +1830,17 @@
       </c>
       <c r="J41" t="str">
         <v/>
+      </c>
+      <c r="K41" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v>SLN1040</v>
       </c>
-      <c r="B42" t="str">
-        <v/>
+      <c r="B42">
+        <v>1</v>
       </c>
       <c r="C42" t="str">
         <v>BB-X HYPER-REPEL α 悬停</v>
@@ -1742,14 +1865,17 @@
       </c>
       <c r="J42" t="str">
         <v/>
+      </c>
+      <c r="K42" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v>SLN1041</v>
       </c>
-      <c r="B43" t="str">
-        <v/>
+      <c r="B43">
+        <v>1</v>
       </c>
       <c r="C43" t="str">
         <v>OCEA 16 30m</v>
@@ -1774,14 +1900,17 @@
       </c>
       <c r="J43" t="str">
         <v/>
+      </c>
+      <c r="K43" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v>SLN1042</v>
       </c>
-      <c r="B44" t="str">
-        <v/>
+      <c r="B44">
+        <v>1</v>
       </c>
       <c r="C44" t="str">
         <v>PITBULL 4+</v>
@@ -1806,14 +1935,17 @@
       </c>
       <c r="J44" t="str">
         <v/>
+      </c>
+      <c r="K44" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
         <v>SLN1043</v>
       </c>
-      <c r="B45" t="str">
-        <v/>
+      <c r="B45">
+        <v>1</v>
       </c>
       <c r="C45" t="str">
         <v>BASIS G5 PE SUSPEND</v>
@@ -1838,14 +1970,17 @@
       </c>
       <c r="J45" t="str">
         <v/>
+      </c>
+      <c r="K45" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
         <v>SLN1044</v>
       </c>
-      <c r="B46" t="str">
-        <v/>
+      <c r="B46">
+        <v>1</v>
       </c>
       <c r="C46" t="str">
         <v>FIREBLOOD STRETCH 悬停</v>
@@ -1870,14 +2005,17 @@
       </c>
       <c r="J46" t="str">
         <v/>
+      </c>
+      <c r="K46" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v>SLN1045</v>
       </c>
-      <c r="B47" t="str">
-        <v/>
+      <c r="B47">
+        <v>1</v>
       </c>
       <c r="C47" t="str">
         <v>SIGHT LASER EX 240m</v>
@@ -1902,14 +2040,17 @@
       </c>
       <c r="J47" t="str">
         <v/>
+      </c>
+      <c r="K47" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v>SLN1046</v>
       </c>
-      <c r="B48" t="str">
-        <v/>
+      <c r="B48">
+        <v>1</v>
       </c>
       <c r="C48" t="str">
         <v>PITBULL G5</v>
@@ -1934,14 +2075,17 @@
       </c>
       <c r="J48" t="str">
         <v/>
+      </c>
+      <c r="K48" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v>SLN1047</v>
       </c>
-      <c r="B49" t="str">
-        <v/>
+      <c r="B49">
+        <v>1</v>
       </c>
       <c r="C49" t="str">
         <v>Soare AJING 150m</v>
@@ -1966,14 +2110,17 @@
       </c>
       <c r="J49" t="str">
         <v/>
+      </c>
+      <c r="K49" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
         <v>SLN1048</v>
       </c>
-      <c r="B50" t="str">
-        <v/>
+      <c r="B50">
+        <v>1</v>
       </c>
       <c r="C50" t="str">
         <v>Sephia MASTER 前导线 30m</v>
@@ -1998,14 +2145,17 @@
       </c>
       <c r="J50" t="str">
         <v/>
+      </c>
+      <c r="K50" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
         <v>SLN1049</v>
       </c>
-      <c r="B51" t="str">
-        <v/>
+      <c r="B51">
+        <v>1</v>
       </c>
       <c r="C51" t="str">
         <v>BB BRAID</v>
@@ -2030,14 +2180,17 @@
       </c>
       <c r="J51" t="str">
         <v/>
+      </c>
+      <c r="K51" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
         <v>SLN1050</v>
       </c>
-      <c r="B52" t="str">
-        <v/>
+      <c r="B52">
+        <v>1</v>
       </c>
       <c r="C52" t="str">
         <v>BAISIS 矶</v>
@@ -2062,14 +2215,17 @@
       </c>
       <c r="J52" t="str">
         <v/>
+      </c>
+      <c r="K52" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
         <v>SLN1051</v>
       </c>
-      <c r="B53" t="str">
-        <v/>
+      <c r="B53">
+        <v>1</v>
       </c>
       <c r="C53" t="str">
         <v>BASIS ORANGE ZERO SUSPEND</v>
@@ -2094,14 +2250,17 @@
       </c>
       <c r="J53" t="str">
         <v/>
+      </c>
+      <c r="K53" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
         <v>SLN1052</v>
       </c>
-      <c r="B54" t="str">
-        <v/>
+      <c r="B54">
+        <v>1</v>
       </c>
       <c r="C54" t="str">
         <v>BAISIS EX</v>
@@ -2126,14 +2285,17 @@
       </c>
       <c r="J54" t="str">
         <v/>
+      </c>
+      <c r="K54" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
         <v>SLN1053</v>
       </c>
-      <c r="B55" t="str">
-        <v/>
+      <c r="B55">
+        <v>1</v>
       </c>
       <c r="C55" t="str">
         <v>EXSENCE 前导线 EX 30m</v>
@@ -2158,14 +2320,17 @@
       </c>
       <c r="J55" t="str">
         <v/>
+      </c>
+      <c r="K55" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
         <v>SLN1054</v>
       </c>
-      <c r="B56" t="str">
-        <v/>
+      <c r="B56">
+        <v>1</v>
       </c>
       <c r="C56" t="str">
         <v>炎月 EX 前导线 30m</v>
@@ -2190,14 +2355,17 @@
       </c>
       <c r="J56" t="str">
         <v/>
+      </c>
+      <c r="K56" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
         <v>SLN1055</v>
       </c>
-      <c r="B57" t="str">
-        <v/>
+      <c r="B57">
+        <v>1</v>
       </c>
       <c r="C57" t="str">
         <v>Soare 前导线 EX 30m</v>
@@ -2222,14 +2390,17 @@
       </c>
       <c r="J57" t="str">
         <v/>
+      </c>
+      <c r="K57" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
         <v>SLN1056</v>
       </c>
-      <c r="B58" t="str">
-        <v/>
+      <c r="B58">
+        <v>1</v>
       </c>
       <c r="C58" t="str">
         <v>Sephia 前导线 30m</v>
@@ -2254,14 +2425,17 @@
       </c>
       <c r="J58" t="str">
         <v/>
+      </c>
+      <c r="K58" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
         <v>SLN1057</v>
       </c>
-      <c r="B59" t="str">
-        <v/>
+      <c r="B59">
+        <v>1</v>
       </c>
       <c r="C59" t="str">
         <v>LIMITED PRO 前导线 悬停</v>
@@ -2286,14 +2460,17 @@
       </c>
       <c r="J59" t="str">
         <v/>
+      </c>
+      <c r="K59" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
         <v>SLN1058</v>
       </c>
-      <c r="B60" t="str">
-        <v/>
+      <c r="B60">
+        <v>1</v>
       </c>
       <c r="C60" t="str">
         <v>PITBULL 8</v>
@@ -2319,10 +2496,13 @@
       <c r="J60" t="str">
         <v/>
       </c>
+      <c r="K60" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K60"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2427,7 +2607,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C3" t="str">
-        <v>Tanatoru 8 PL-F58R</v>
+        <v>Tanatoru 8 PL-F58R | 1号</v>
       </c>
       <c r="D3" t="str">
         <v>5色</v>
@@ -2471,7 +2651,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C4" t="str">
-        <v>Tanatoru 8 PL-F58R</v>
+        <v>Tanatoru 8 PL-F58R | 1.5号</v>
       </c>
       <c r="D4" t="str">
         <v>5色</v>
@@ -2515,7 +2695,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C5" t="str">
-        <v>Tanatoru 8 PL-F58R</v>
+        <v>Tanatoru 8 PL-F58R | 2号</v>
       </c>
       <c r="D5" t="str">
         <v>5色</v>
@@ -2603,7 +2783,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C7" t="str">
-        <v>Tanatoru 8 PL-F68R</v>
+        <v>Tanatoru 8 PL-F68R | 0.8号</v>
       </c>
       <c r="D7" t="str">
         <v>5色</v>
@@ -2647,7 +2827,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C8" t="str">
-        <v>Tanatoru 8 PL-F68R</v>
+        <v>Tanatoru 8 PL-F68R | 1号</v>
       </c>
       <c r="D8" t="str">
         <v>5色</v>
@@ -2691,7 +2871,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C9" t="str">
-        <v>Tanatoru 8 PL-F68R</v>
+        <v>Tanatoru 8 PL-F68R | 1.5号</v>
       </c>
       <c r="D9" t="str">
         <v>5色</v>
@@ -2735,7 +2915,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C10" t="str">
-        <v>Tanatoru 8 PL-F68R</v>
+        <v>Tanatoru 8 PL-F68R | 2号</v>
       </c>
       <c r="D10" t="str">
         <v>5色</v>
@@ -2779,7 +2959,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C11" t="str">
-        <v>Tanatoru 8 PL-F68R</v>
+        <v>Tanatoru 8 PL-F68R | 3号</v>
       </c>
       <c r="D11" t="str">
         <v>5色</v>
@@ -2867,7 +3047,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C13" t="str">
-        <v>Tanatoru 8 PL-F78R</v>
+        <v>Tanatoru 8 PL-F78R | 0.8号</v>
       </c>
       <c r="D13" t="str">
         <v>5色</v>
@@ -2911,7 +3091,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C14" t="str">
-        <v>Tanatoru 8 PL-F78R</v>
+        <v>Tanatoru 8 PL-F78R | 1号</v>
       </c>
       <c r="D14" t="str">
         <v>5色</v>
@@ -2955,7 +3135,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C15" t="str">
-        <v>Tanatoru 8 PL-F78R</v>
+        <v>Tanatoru 8 PL-F78R | 1.5号</v>
       </c>
       <c r="D15" t="str">
         <v>5色</v>
@@ -2999,7 +3179,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C16" t="str">
-        <v>Tanatoru 8 PL-F78R</v>
+        <v>Tanatoru 8 PL-F78R | 2号</v>
       </c>
       <c r="D16" t="str">
         <v>5色</v>
@@ -3043,7 +3223,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C17" t="str">
-        <v>Tanatoru 8 PL-F78R</v>
+        <v>Tanatoru 8 PL-F78R | 3号</v>
       </c>
       <c r="D17" t="str">
         <v>5色</v>
@@ -3087,7 +3267,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C18" t="str">
-        <v>Tanatoru 8 PL-F78R</v>
+        <v>Tanatoru 8 PL-F78R | 4号</v>
       </c>
       <c r="D18" t="str">
         <v>5色</v>
@@ -3175,7 +3355,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C20" t="str">
-        <v>Tanatoru 8 PL-F78R</v>
+        <v>Tanatoru 8 PL-F78R | 5号</v>
       </c>
       <c r="D20" t="str">
         <v>5色</v>
@@ -3219,7 +3399,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C21" t="str">
-        <v>Tanatoru 8 PL-F78R</v>
+        <v>Tanatoru 8 PL-F78R | 6号</v>
       </c>
       <c r="D21" t="str">
         <v>5色</v>
@@ -3263,7 +3443,7 @@
         <v>SLN1000</v>
       </c>
       <c r="C22" t="str">
-        <v>Tanatoru 8 PL-F88S</v>
+        <v>Tanatoru 8 PL-F88S | 4号</v>
       </c>
       <c r="D22" t="str">
         <v>5色</v>
@@ -3351,7 +3531,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C24" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F94R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F94R | 3号</v>
       </c>
       <c r="D24" t="str">
         <v>5色</v>
@@ -3395,7 +3575,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C25" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F94R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F94R | 4号</v>
       </c>
       <c r="D25" t="str">
         <v>5色</v>
@@ -3439,7 +3619,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C26" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F94R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F94R | 5号</v>
       </c>
       <c r="D26" t="str">
         <v>5色</v>
@@ -3527,7 +3707,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C28" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 0.8号</v>
       </c>
       <c r="D28" t="str">
         <v>5色</v>
@@ -3571,7 +3751,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C29" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 1号</v>
       </c>
       <c r="D29" t="str">
         <v>5色</v>
@@ -3615,7 +3795,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C30" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 1.5号</v>
       </c>
       <c r="D30" t="str">
         <v>5色</v>
@@ -3659,7 +3839,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C31" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 2号</v>
       </c>
       <c r="D31" t="str">
         <v>5色</v>
@@ -3703,7 +3883,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C32" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 3号</v>
       </c>
       <c r="D32" t="str">
         <v>5色</v>
@@ -3747,7 +3927,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C33" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 4号</v>
       </c>
       <c r="D33" t="str">
         <v>5色</v>
@@ -3791,7 +3971,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C34" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 5号</v>
       </c>
       <c r="D34" t="str">
         <v>5色</v>
@@ -3835,7 +4015,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C35" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 6号</v>
       </c>
       <c r="D35" t="str">
         <v>5色</v>
@@ -3879,7 +4059,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C36" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 8号</v>
       </c>
       <c r="D36" t="str">
         <v>5色</v>
@@ -3923,7 +4103,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C37" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 10号</v>
       </c>
       <c r="D37" t="str">
         <v>5色</v>
@@ -3967,7 +4147,7 @@
         <v>SLN1001</v>
       </c>
       <c r="C38" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R</v>
+        <v>Tanatoru 4 / 8 100m  连盘 PL-F98R | 12号</v>
       </c>
       <c r="D38" t="str">
         <v>5色</v>
@@ -4143,7 +4323,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C42" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m</v>
       </c>
       <c r="D42" t="str">
         <v>暗棕色</v>
@@ -4187,7 +4367,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C43" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 19.5lb</v>
       </c>
       <c r="D43" t="str">
         <v>暗棕色</v>
@@ -4231,7 +4411,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C44" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 23.7lb</v>
       </c>
       <c r="D44" t="str">
         <v>暗棕色</v>
@@ -4275,7 +4455,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C45" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 27.7lb</v>
       </c>
       <c r="D45" t="str">
         <v>暗棕色</v>
@@ -4319,7 +4499,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C46" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 35.2lb</v>
       </c>
       <c r="D46" t="str">
         <v>暗棕色</v>
@@ -4363,7 +4543,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C47" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 12.3lb</v>
       </c>
       <c r="D47" t="str">
         <v>粉色</v>
@@ -4407,7 +4587,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C48" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 13.9lb</v>
       </c>
       <c r="D48" t="str">
         <v>粉色</v>
@@ -4451,7 +4631,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C49" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 19.5lb | 168849</v>
       </c>
       <c r="D49" t="str">
         <v>粉色</v>
@@ -4495,7 +4675,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C50" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 23.7lb | 168856</v>
       </c>
       <c r="D50" t="str">
         <v>粉色</v>
@@ -4539,7 +4719,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C51" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 27.7lb | 168863</v>
       </c>
       <c r="D51" t="str">
         <v>粉色</v>
@@ -4583,7 +4763,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C52" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 35.2lb | 168870</v>
       </c>
       <c r="D52" t="str">
         <v>粉色</v>
@@ -4671,7 +4851,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C54" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m</v>
       </c>
       <c r="D54" t="str">
         <v>暗棕色</v>
@@ -4715,7 +4895,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C55" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 19.5lb</v>
       </c>
       <c r="D55" t="str">
         <v>暗棕色</v>
@@ -4759,7 +4939,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C56" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 23.7lb</v>
       </c>
       <c r="D56" t="str">
         <v>暗棕色</v>
@@ -4803,7 +4983,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C57" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 27.7lb</v>
       </c>
       <c r="D57" t="str">
         <v>暗棕色</v>
@@ -4847,7 +5027,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C58" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 35.2lb</v>
       </c>
       <c r="D58" t="str">
         <v>暗棕色</v>
@@ -4891,7 +5071,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C59" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 12.3lb</v>
       </c>
       <c r="D59" t="str">
         <v>粉色</v>
@@ -4935,7 +5115,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C60" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 13.9lb</v>
       </c>
       <c r="D60" t="str">
         <v>粉色</v>
@@ -4979,7 +5159,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C61" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 19.5lb | 168962</v>
       </c>
       <c r="D61" t="str">
         <v>粉色</v>
@@ -5023,7 +5203,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C62" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 23.7lb | 168979</v>
       </c>
       <c r="D62" t="str">
         <v>粉色</v>
@@ -5067,7 +5247,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C63" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 27.7lb | 168986</v>
       </c>
       <c r="D63" t="str">
         <v>粉色</v>
@@ -5111,7 +5291,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C64" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 35.2lb | 168993</v>
       </c>
       <c r="D64" t="str">
         <v>粉色</v>
@@ -5155,7 +5335,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C65" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 11.2lb</v>
       </c>
       <c r="D65" t="str">
         <v>暗棕色</v>
@@ -5199,7 +5379,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C66" t="str">
-        <v>PITBULL G9 LD-M49Z</v>
+        <v>PITBULL G9 LD-M49Z | 100m | 11.2lb | 169013</v>
       </c>
       <c r="D66" t="str">
         <v>粉色</v>
@@ -5243,7 +5423,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C67" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 11.2lb</v>
       </c>
       <c r="D67" t="str">
         <v>暗棕色</v>
@@ -5287,7 +5467,7 @@
         <v>SLN1002</v>
       </c>
       <c r="C68" t="str">
-        <v>PITBULL G9 LD-M59Z</v>
+        <v>PITBULL G9 LD-M59Z | 150m | 11.2lb | 169037</v>
       </c>
       <c r="D68" t="str">
         <v>粉色</v>
@@ -5375,7 +5555,7 @@
         <v>SLN1003</v>
       </c>
       <c r="C70" t="str">
-        <v>OCEA PLUGGER NYLON LEADER LA-A51Z</v>
+        <v>OCEA PLUGGER NYLON LEADER LA-A51Z | 35号</v>
       </c>
       <c r="D70" t="str">
         <v>透明色</v>
@@ -5419,7 +5599,7 @@
         <v>SLN1003</v>
       </c>
       <c r="C71" t="str">
-        <v>OCEA PLUGGER NYLON LEADER LA-A51Z</v>
+        <v>OCEA PLUGGER NYLON LEADER LA-A51Z | 40号</v>
       </c>
       <c r="D71" t="str">
         <v>透明色</v>
@@ -5463,7 +5643,7 @@
         <v>SLN1003</v>
       </c>
       <c r="C72" t="str">
-        <v>OCEA PLUGGER NYLON LEADER LA-A51Z</v>
+        <v>OCEA PLUGGER NYLON LEADER LA-A51Z | 50号</v>
       </c>
       <c r="D72" t="str">
         <v>透明色</v>
@@ -5507,7 +5687,7 @@
         <v>SLN1003</v>
       </c>
       <c r="C73" t="str">
-        <v>OCEA PLUGGER NYLON LEADER LA-A51Z</v>
+        <v>OCEA PLUGGER NYLON LEADER LA-A51Z | 60号</v>
       </c>
       <c r="D73" t="str">
         <v>透明色</v>
@@ -5551,7 +5731,7 @@
         <v>SLN1003</v>
       </c>
       <c r="C74" t="str">
-        <v>OCEA PLUGGER NYLON LEADER LA-A51Z</v>
+        <v>OCEA PLUGGER NYLON LEADER LA-A51Z | 70号</v>
       </c>
       <c r="D74" t="str">
         <v>透明色</v>
@@ -5595,7 +5775,7 @@
         <v>SLN1003</v>
       </c>
       <c r="C75" t="str">
-        <v>OCEA PLUGGER NYLON LEADER LA-A51Z</v>
+        <v>OCEA PLUGGER NYLON LEADER LA-A51Z | 22号</v>
       </c>
       <c r="D75" t="str">
         <v>透明色</v>
@@ -5639,7 +5819,7 @@
         <v>SLN1003</v>
       </c>
       <c r="C76" t="str">
-        <v>OCEA PLUGGER NYLON LEADER LA-A51Z</v>
+        <v>OCEA PLUGGER NYLON LEADER LA-A51Z | 26号</v>
       </c>
       <c r="D76" t="str">
         <v>透明色</v>
@@ -5727,7 +5907,7 @@
         <v>SLN1004</v>
       </c>
       <c r="C78" t="str">
-        <v>PITBULL FLUORO LEADER LB-M31Z</v>
+        <v>PITBULL FLUORO LEADER LB-M31Z | 3号</v>
       </c>
       <c r="D78" t="str">
         <v>透明色</v>
@@ -5771,7 +5951,7 @@
         <v>SLN1004</v>
       </c>
       <c r="C79" t="str">
-        <v>PITBULL FLUORO LEADER LB-M31Z</v>
+        <v>PITBULL FLUORO LEADER LB-M31Z | 4号</v>
       </c>
       <c r="D79" t="str">
         <v>透明色</v>
@@ -5815,7 +5995,7 @@
         <v>SLN1004</v>
       </c>
       <c r="C80" t="str">
-        <v>PITBULL FLUORO LEADER LB-M31Z</v>
+        <v>PITBULL FLUORO LEADER LB-M31Z | 5号</v>
       </c>
       <c r="D80" t="str">
         <v>透明色</v>
@@ -5859,7 +6039,7 @@
         <v>SLN1004</v>
       </c>
       <c r="C81" t="str">
-        <v>PITBULL FLUORO LEADER LB-M31Z</v>
+        <v>PITBULL FLUORO LEADER LB-M31Z | 6号</v>
       </c>
       <c r="D81" t="str">
         <v>透明色</v>
@@ -5903,7 +6083,7 @@
         <v>SLN1004</v>
       </c>
       <c r="C82" t="str">
-        <v>PITBULL FLUORO LEADER LB-M31Z</v>
+        <v>PITBULL FLUORO LEADER LB-M31Z | 8号</v>
       </c>
       <c r="D82" t="str">
         <v>透明色</v>
@@ -5947,7 +6127,7 @@
         <v>SLN1004</v>
       </c>
       <c r="C83" t="str">
-        <v>PITBULL FLUORO LEADER LB-M31Z</v>
+        <v>PITBULL FLUORO LEADER LB-M31Z | 7号</v>
       </c>
       <c r="D83" t="str">
         <v>透明色</v>
@@ -5991,7 +6171,7 @@
         <v>SLN1004</v>
       </c>
       <c r="C84" t="str">
-        <v>PITBULL FLUORO LEADER LB-M31Z</v>
+        <v>PITBULL FLUORO LEADER LB-M31Z | 10号</v>
       </c>
       <c r="D84" t="str">
         <v>透明色</v>
@@ -6079,7 +6259,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C86" t="str">
-        <v>OCEA 17+ LD-A71Y</v>
+        <v>OCEA 17+ LD-A71Y | 6号</v>
       </c>
       <c r="D86" t="str">
         <v>10m x 5色</v>
@@ -6123,7 +6303,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C87" t="str">
-        <v>OCEA 17+ LD-A71Y</v>
+        <v>OCEA 17+ LD-A71Y | 8号</v>
       </c>
       <c r="D87" t="str">
         <v>10m x 5色</v>
@@ -6167,7 +6347,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C88" t="str">
-        <v>OCEA 17+ LD-A71Y</v>
+        <v>OCEA 17+ LD-A71Y | 10号</v>
       </c>
       <c r="D88" t="str">
         <v>10m x 5色</v>
@@ -6211,7 +6391,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C89" t="str">
-        <v>OCEA 17+ LD-A71Y</v>
+        <v>OCEA 17+ LD-A71Y | 12号</v>
       </c>
       <c r="D89" t="str">
         <v>10m x 5色</v>
@@ -6255,7 +6435,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C90" t="str">
-        <v>OCEA 17+ LD-A71Y</v>
+        <v>OCEA 17+ LD-A71Y | 5号</v>
       </c>
       <c r="D90" t="str">
         <v>蓝色</v>
@@ -6299,7 +6479,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C91" t="str">
-        <v>OCEA 17+ LD-A71Y</v>
+        <v>OCEA 17+ LD-A71Y | 6号 | 300m</v>
       </c>
       <c r="D91" t="str">
         <v>蓝色</v>
@@ -6343,7 +6523,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C92" t="str">
-        <v>OCEA 17+ LD-A71Y</v>
+        <v>OCEA 17+ LD-A71Y | 8号 | 300m</v>
       </c>
       <c r="D92" t="str">
         <v>蓝色</v>
@@ -6431,7 +6611,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C94" t="str">
-        <v>OCEA 17+ LD-A91Y</v>
+        <v>OCEA 17+ LD-A91Y | 8号</v>
       </c>
       <c r="D94" t="str">
         <v>10m x 5色</v>
@@ -6475,7 +6655,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C95" t="str">
-        <v>OCEA 17+ LD-A91Y</v>
+        <v>OCEA 17+ LD-A91Y | 10号</v>
       </c>
       <c r="D95" t="str">
         <v>10m x 5色</v>
@@ -6519,7 +6699,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C96" t="str">
-        <v>OCEA 17+ LD-A91Y</v>
+        <v>OCEA 17+ LD-A91Y | 12号</v>
       </c>
       <c r="D96" t="str">
         <v>10m x 5色</v>
@@ -6563,7 +6743,7 @@
         <v>SLN1005</v>
       </c>
       <c r="C97" t="str">
-        <v>OCEA 17+ LD-A91Y</v>
+        <v>OCEA 17+ LD-A91Y | 15号</v>
       </c>
       <c r="D97" t="str">
         <v>10m x 5色</v>
@@ -6695,7 +6875,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C100" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 2号</v>
       </c>
       <c r="D100" t="str">
         <v>5色</v>
@@ -6739,7 +6919,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C101" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 3号</v>
       </c>
       <c r="D101" t="str">
         <v>5色</v>
@@ -6783,7 +6963,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C102" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 4号</v>
       </c>
       <c r="D102" t="str">
         <v>5色</v>
@@ -6827,7 +7007,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C103" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 5号</v>
       </c>
       <c r="D103" t="str">
         <v>5色</v>
@@ -6871,7 +7051,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C104" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 6号</v>
       </c>
       <c r="D104" t="str">
         <v>5色</v>
@@ -6915,7 +7095,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C105" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 8号</v>
       </c>
       <c r="D105" t="str">
         <v>5色</v>
@@ -6959,7 +7139,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C106" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 10号</v>
       </c>
       <c r="D106" t="str">
         <v>5色</v>
@@ -7003,7 +7183,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C107" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 12号</v>
       </c>
       <c r="D107" t="str">
         <v>5色</v>
@@ -7047,7 +7227,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C108" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 5号 | 300m</v>
       </c>
       <c r="D108" t="str">
         <v>蓝色</v>
@@ -7091,7 +7271,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C109" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 6号 | 300m</v>
       </c>
       <c r="D109" t="str">
         <v>蓝色</v>
@@ -7135,7 +7315,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C110" t="str">
-        <v>OCEA 8 LD-A71S</v>
+        <v>OCEA 8 LD-A71S | 8号 | 300m</v>
       </c>
       <c r="D110" t="str">
         <v>蓝色</v>
@@ -7223,7 +7403,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C112" t="str">
-        <v>OCEA 8 LD-A81S</v>
+        <v>OCEA 8 LD-A81S | 3号</v>
       </c>
       <c r="D112" t="str">
         <v>5色</v>
@@ -7267,7 +7447,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C113" t="str">
-        <v>OCEA 8 LD-A81S</v>
+        <v>OCEA 8 LD-A81S | 4号</v>
       </c>
       <c r="D113" t="str">
         <v>5色</v>
@@ -7311,7 +7491,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C114" t="str">
-        <v>OCEA 8 LD-A81S</v>
+        <v>OCEA 8 LD-A81S | 5号</v>
       </c>
       <c r="D114" t="str">
         <v>5色</v>
@@ -7355,7 +7535,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C115" t="str">
-        <v>OCEA 8 LD-A81S</v>
+        <v>OCEA 8 LD-A81S | 6号</v>
       </c>
       <c r="D115" t="str">
         <v>5色</v>
@@ -7399,7 +7579,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C116" t="str">
-        <v>OCEA 8 LD-A81S</v>
+        <v>OCEA 8 LD-A81S | 8号</v>
       </c>
       <c r="D116" t="str">
         <v>5色</v>
@@ -7443,7 +7623,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C117" t="str">
-        <v>OCEA 8 LD-A81S</v>
+        <v>OCEA 8 LD-A81S | 10号</v>
       </c>
       <c r="D117" t="str">
         <v>5色</v>
@@ -7487,7 +7667,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C118" t="str">
-        <v>OCEA 8 LD-A81S</v>
+        <v>OCEA 8 LD-A81S | 12号</v>
       </c>
       <c r="D118" t="str">
         <v>5色</v>
@@ -7575,7 +7755,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C120" t="str">
-        <v>OCEA 8 LD-A91S</v>
+        <v>OCEA 8 LD-A91S | 3号</v>
       </c>
       <c r="D120" t="str">
         <v>5色</v>
@@ -7619,7 +7799,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C121" t="str">
-        <v>OCEA 8 LD-A91S</v>
+        <v>OCEA 8 LD-A91S | 5号</v>
       </c>
       <c r="D121" t="str">
         <v>5色</v>
@@ -7663,7 +7843,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C122" t="str">
-        <v>OCEA 8 LD-A91S</v>
+        <v>OCEA 8 LD-A91S | 6号</v>
       </c>
       <c r="D122" t="str">
         <v>5色</v>
@@ -7707,7 +7887,7 @@
         <v>SLN1006</v>
       </c>
       <c r="C123" t="str">
-        <v>OCEA 8 LD-A91S</v>
+        <v>OCEA 8 LD-A91S | 10号</v>
       </c>
       <c r="D123" t="str">
         <v>5色</v>
@@ -7795,7 +7975,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C125" t="str">
-        <v>OCEA JIGGER MX4 PL-O14X</v>
+        <v>OCEA JIGGER MX4 PL-O14X | 1.2号</v>
       </c>
       <c r="D125" t="str">
         <v>10m x 5色</v>
@@ -7839,7 +8019,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C126" t="str">
-        <v>OCEA JIGGER MX4 PL-O14X</v>
+        <v>OCEA JIGGER MX4 PL-O14X | 1.5号</v>
       </c>
       <c r="D126" t="str">
         <v>10m x 5色</v>
@@ -7883,7 +8063,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C127" t="str">
-        <v>OCEA JIGGER MX4 PL-O14X</v>
+        <v>OCEA JIGGER MX4 PL-O14X | 2号</v>
       </c>
       <c r="D127" t="str">
         <v>10m x 5色</v>
@@ -7927,7 +8107,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C128" t="str">
-        <v>OCEA JIGGER MX4 PL-O14X</v>
+        <v>OCEA JIGGER MX4 PL-O14X | 2.5号</v>
       </c>
       <c r="D128" t="str">
         <v>10m x 5色</v>
@@ -7971,7 +8151,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C129" t="str">
-        <v>OCEA JIGGER MX4 PL-O14X</v>
+        <v>OCEA JIGGER MX4 PL-O14X | 3号</v>
       </c>
       <c r="D129" t="str">
         <v>10m x 5色</v>
@@ -8015,7 +8195,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C130" t="str">
-        <v>OCEA JIGGER MX4 PL-O14X</v>
+        <v>OCEA JIGGER MX4 PL-O14X | 4号</v>
       </c>
       <c r="D130" t="str">
         <v>10m x 5色</v>
@@ -8103,7 +8283,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C132" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 0.8号</v>
       </c>
       <c r="D132" t="str">
         <v>绿色</v>
@@ -8147,7 +8327,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C133" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 1号</v>
       </c>
       <c r="D133" t="str">
         <v>绿色</v>
@@ -8191,7 +8371,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C134" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 1.2号</v>
       </c>
       <c r="D134" t="str">
         <v>绿色</v>
@@ -8235,7 +8415,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C135" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 1.5号</v>
       </c>
       <c r="D135" t="str">
         <v>绿色</v>
@@ -8279,7 +8459,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C136" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 2号</v>
       </c>
       <c r="D136" t="str">
         <v>绿色</v>
@@ -8323,7 +8503,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C137" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 2.5号</v>
       </c>
       <c r="D137" t="str">
         <v>绿色</v>
@@ -8367,7 +8547,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C138" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 3号</v>
       </c>
       <c r="D138" t="str">
         <v>绿色</v>
@@ -8411,7 +8591,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C139" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 4号</v>
       </c>
       <c r="D139" t="str">
         <v>绿色</v>
@@ -8455,7 +8635,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C140" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 0.8号 | 300m</v>
       </c>
       <c r="D140" t="str">
         <v>10m x 5色</v>
@@ -8499,7 +8679,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C141" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 1号 | 300m</v>
       </c>
       <c r="D141" t="str">
         <v>10m x 5色</v>
@@ -8543,7 +8723,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C142" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 1.2号 | 300m</v>
       </c>
       <c r="D142" t="str">
         <v>10m x 5色</v>
@@ -8587,7 +8767,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C143" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 1.5号 | 300m</v>
       </c>
       <c r="D143" t="str">
         <v>10m x 5色</v>
@@ -8631,7 +8811,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C144" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 2号 | 300m</v>
       </c>
       <c r="D144" t="str">
         <v>10m x 5色</v>
@@ -8675,7 +8855,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C145" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 2.5号 | 300m</v>
       </c>
       <c r="D145" t="str">
         <v>10m x 5色</v>
@@ -8719,7 +8899,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C146" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 3号 | 300m</v>
       </c>
       <c r="D146" t="str">
         <v>10m x 5色</v>
@@ -8763,7 +8943,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C147" t="str">
-        <v>OCEA JIGGER MX4 PL-O74P</v>
+        <v>OCEA JIGGER MX4 PL-O74P | 4号 | 300m</v>
       </c>
       <c r="D147" t="str">
         <v>10m x 5色</v>
@@ -8851,7 +9031,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C149" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 1.2号</v>
       </c>
       <c r="D149" t="str">
         <v>绿色</v>
@@ -8895,7 +9075,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C150" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 1.5号</v>
       </c>
       <c r="D150" t="str">
         <v>绿色</v>
@@ -8939,7 +9119,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C151" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 2号</v>
       </c>
       <c r="D151" t="str">
         <v>绿色</v>
@@ -8983,7 +9163,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C152" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 2.5号</v>
       </c>
       <c r="D152" t="str">
         <v>绿色</v>
@@ -9027,7 +9207,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C153" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 3号</v>
       </c>
       <c r="D153" t="str">
         <v>绿色</v>
@@ -9071,7 +9251,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C154" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 4号</v>
       </c>
       <c r="D154" t="str">
         <v>绿色</v>
@@ -9115,7 +9295,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C155" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 1号</v>
       </c>
       <c r="D155" t="str">
         <v>10m x 5色</v>
@@ -9159,7 +9339,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C156" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 1.2号 | 600m</v>
       </c>
       <c r="D156" t="str">
         <v>10m x 5色</v>
@@ -9203,7 +9383,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C157" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 1.5号 | 600m</v>
       </c>
       <c r="D157" t="str">
         <v>10m x 5色</v>
@@ -9247,7 +9427,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C158" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 2号 | 600m</v>
       </c>
       <c r="D158" t="str">
         <v>10m x 5色</v>
@@ -9291,7 +9471,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C159" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 2.5号 | 600m</v>
       </c>
       <c r="D159" t="str">
         <v>10m x 5色</v>
@@ -9335,7 +9515,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C160" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 3号 | 600m</v>
       </c>
       <c r="D160" t="str">
         <v>10m x 5色</v>
@@ -9379,7 +9559,7 @@
         <v>SLN1007</v>
       </c>
       <c r="C161" t="str">
-        <v>OCEA JIGGER MX4 PL-O94P</v>
+        <v>OCEA JIGGER MX4 PL-O94P | 4号 | 600m</v>
       </c>
       <c r="D161" t="str">
         <v>10m x 5色</v>
@@ -9467,7 +9647,7 @@
         <v>SLN1008</v>
       </c>
       <c r="C163" t="str">
-        <v>KISU SPECIAL EX4 PL-N61Q</v>
+        <v>KISU SPECIAL EX4 PL-N61Q | 213m</v>
       </c>
       <c r="D163" t="str">
         <v>5色</v>
@@ -9511,7 +9691,7 @@
         <v>SLN1008</v>
       </c>
       <c r="C164" t="str">
-        <v>KISU SPECIAL EX4 PL-N61Q</v>
+        <v>KISU SPECIAL EX4 PL-N61Q | 213m | 526779</v>
       </c>
       <c r="D164" t="str">
         <v>5色</v>
@@ -9599,7 +9779,7 @@
         <v>SLN1008</v>
       </c>
       <c r="C166" t="str">
-        <v>KISU SPECIAL EX4 PL-N71Q</v>
+        <v>KISU SPECIAL EX4 PL-N71Q | 263m</v>
       </c>
       <c r="D166" t="str">
         <v>5色</v>
@@ -9643,7 +9823,7 @@
         <v>SLN1008</v>
       </c>
       <c r="C167" t="str">
-        <v>KISU SPECIAL EX4 PL-N71Q</v>
+        <v>KISU SPECIAL EX4 PL-N71Q | 263m | 526809</v>
       </c>
       <c r="D167" t="str">
         <v>5色</v>
@@ -9731,7 +9911,7 @@
         <v>SLN1009</v>
       </c>
       <c r="C169" t="str">
-        <v>KISU SPECIAL G5 LD-N61T</v>
+        <v>KISU SPECIAL G5 LD-N61T | 200m</v>
       </c>
       <c r="D169" t="str">
         <v>5色</v>
@@ -9775,7 +9955,7 @@
         <v>SLN1009</v>
       </c>
       <c r="C170" t="str">
-        <v>KISU SPECIAL G5 LD-N61T</v>
+        <v>KISU SPECIAL G5 LD-N61T | 200m | 695086</v>
       </c>
       <c r="D170" t="str">
         <v>5色</v>
@@ -9863,7 +10043,7 @@
         <v>SLN1009</v>
       </c>
       <c r="C172" t="str">
-        <v>KISU SPECIAL G5 LD-N71T</v>
+        <v>KISU SPECIAL G5 LD-N71T | 250m</v>
       </c>
       <c r="D172" t="str">
         <v>5色</v>
@@ -9951,7 +10131,7 @@
         <v>SLN1010</v>
       </c>
       <c r="C174" t="str">
-        <v>OCEA EX 前导线 CL-O26L</v>
+        <v>OCEA EX 前导线 CL-O26L | 5号</v>
       </c>
       <c r="D174" t="str">
         <v>透明色</v>
@@ -9995,7 +10175,7 @@
         <v>SLN1010</v>
       </c>
       <c r="C175" t="str">
-        <v>OCEA EX 前导线 CL-O26L</v>
+        <v>OCEA EX 前导线 CL-O26L | 6号</v>
       </c>
       <c r="D175" t="str">
         <v>透明色</v>
@@ -10083,7 +10263,7 @@
         <v>SLN1010</v>
       </c>
       <c r="C177" t="str">
-        <v>OCEA EX 前导线 CL-O36L</v>
+        <v>OCEA EX 前导线 CL-O36L | 12号</v>
       </c>
       <c r="D177" t="str">
         <v>透明色</v>
@@ -10127,7 +10307,7 @@
         <v>SLN1010</v>
       </c>
       <c r="C178" t="str">
-        <v>OCEA EX 前导线 CL-O36L</v>
+        <v>OCEA EX 前导线 CL-O36L | 14号</v>
       </c>
       <c r="D178" t="str">
         <v>透明色</v>
@@ -10171,7 +10351,7 @@
         <v>SLN1010</v>
       </c>
       <c r="C179" t="str">
-        <v>OCEA EX 前导线 CL-O36L</v>
+        <v>OCEA EX 前导线 CL-O36L | 18号</v>
       </c>
       <c r="D179" t="str">
         <v>透明色</v>
@@ -10215,7 +10395,7 @@
         <v>SLN1010</v>
       </c>
       <c r="C180" t="str">
-        <v>OCEA EX 前导线 CL-O36L</v>
+        <v>OCEA EX 前导线 CL-O36L | 22号</v>
       </c>
       <c r="D180" t="str">
         <v>透明色</v>
@@ -10259,7 +10439,7 @@
         <v>SLN1010</v>
       </c>
       <c r="C181" t="str">
-        <v>OCEA EX 前导线 CL-O36L</v>
+        <v>OCEA EX 前导线 CL-O36L | 30号</v>
       </c>
       <c r="D181" t="str">
         <v>透明色</v>
@@ -10347,7 +10527,7 @@
         <v>SLN1011</v>
       </c>
       <c r="C183" t="str">
-        <v>LIMITED PRO G5+ PE PL-I55Q</v>
+        <v>LIMITED PRO G5+ PE PL-I55Q | 0.8号</v>
       </c>
       <c r="D183" t="str">
         <v>黄色</v>
@@ -10391,7 +10571,7 @@
         <v>SLN1011</v>
       </c>
       <c r="C184" t="str">
-        <v>LIMITED PRO G5+ PE PL-I55Q</v>
+        <v>LIMITED PRO G5+ PE PL-I55Q | 1号</v>
       </c>
       <c r="D184" t="str">
         <v>黄色</v>
@@ -10435,7 +10615,7 @@
         <v>SLN1011</v>
       </c>
       <c r="C185" t="str">
-        <v>LIMITED PRO G5+ PE PL-I55Q</v>
+        <v>LIMITED PRO G5+ PE PL-I55Q | 0.6号</v>
       </c>
       <c r="D185" t="str">
         <v>红色</v>
@@ -10479,7 +10659,7 @@
         <v>SLN1011</v>
       </c>
       <c r="C186" t="str">
-        <v>LIMITED PRO G5+ PE PL-I55Q</v>
+        <v>LIMITED PRO G5+ PE PL-I55Q | 0.8号 | 150m</v>
       </c>
       <c r="D186" t="str">
         <v>红色</v>
@@ -10523,7 +10703,7 @@
         <v>SLN1011</v>
       </c>
       <c r="C187" t="str">
-        <v>LIMITED PRO G5+ PE PL-I55Q</v>
+        <v>LIMITED PRO G5+ PE PL-I55Q | 1号 | 150m</v>
       </c>
       <c r="D187" t="str">
         <v>红色</v>
@@ -10611,7 +10791,7 @@
         <v>SLN1011</v>
       </c>
       <c r="C189" t="str">
-        <v>LIMITED PRO G5+ PE PL-I65R</v>
+        <v>LIMITED PRO G5+ PE PL-I65R | 1号</v>
       </c>
       <c r="D189" t="str">
         <v>黄色</v>
@@ -10655,7 +10835,7 @@
         <v>SLN1011</v>
       </c>
       <c r="C190" t="str">
-        <v>LIMITED PRO G5+ PE PL-I65R</v>
+        <v>LIMITED PRO G5+ PE PL-I65R | 1.5号</v>
       </c>
       <c r="D190" t="str">
         <v>黄色</v>
@@ -10699,7 +10879,7 @@
         <v>SLN1011</v>
       </c>
       <c r="C191" t="str">
-        <v>LIMITED PRO G5+ PE PL-I65R</v>
+        <v>LIMITED PRO G5+ PE PL-I65R | 0.8号</v>
       </c>
       <c r="D191" t="str">
         <v>红色</v>
@@ -10743,7 +10923,7 @@
         <v>SLN1011</v>
       </c>
       <c r="C192" t="str">
-        <v>LIMITED PRO G5+ PE PL-I65R</v>
+        <v>LIMITED PRO G5+ PE PL-I65R | 1号 | 200m</v>
       </c>
       <c r="D192" t="str">
         <v>红色</v>
@@ -10787,7 +10967,7 @@
         <v>SLN1011</v>
       </c>
       <c r="C193" t="str">
-        <v>LIMITED PRO G5+ PE PL-I65R</v>
+        <v>LIMITED PRO G5+ PE PL-I65R | 1.5号 | 200m</v>
       </c>
       <c r="D193" t="str">
         <v>红色</v>
@@ -10875,7 +11055,7 @@
         <v>SLN1012</v>
       </c>
       <c r="C195" t="str">
-        <v>PITBULL 12 PL-76FV</v>
+        <v>PITBULL 12 PL-76FV | 0.8号</v>
       </c>
       <c r="D195" t="str">
         <v>绿色</v>
@@ -10919,7 +11099,7 @@
         <v>SLN1012</v>
       </c>
       <c r="C196" t="str">
-        <v>PITBULL 12 PL-76FV</v>
+        <v>PITBULL 12 PL-76FV | 1号</v>
       </c>
       <c r="D196" t="str">
         <v>绿色</v>
@@ -10963,7 +11143,7 @@
         <v>SLN1012</v>
       </c>
       <c r="C197" t="str">
-        <v>PITBULL 12 PL-76FV</v>
+        <v>PITBULL 12 PL-76FV | 1.2号</v>
       </c>
       <c r="D197" t="str">
         <v>绿色</v>
@@ -11007,7 +11187,7 @@
         <v>SLN1012</v>
       </c>
       <c r="C198" t="str">
-        <v>PITBULL 12 PL-76FV</v>
+        <v>PITBULL 12 PL-76FV | 1.5号</v>
       </c>
       <c r="D198" t="str">
         <v>绿色</v>
@@ -11051,7 +11231,7 @@
         <v>SLN1012</v>
       </c>
       <c r="C199" t="str">
-        <v>PITBULL 12 PL-76FV</v>
+        <v>PITBULL 12 PL-76FV | 2号</v>
       </c>
       <c r="D199" t="str">
         <v>绿色</v>
@@ -11139,7 +11319,7 @@
         <v>SLN1012</v>
       </c>
       <c r="C201" t="str">
-        <v>PITBULL 12 PL-77FV</v>
+        <v>PITBULL 12 PL-77FV | 0.8号</v>
       </c>
       <c r="D201" t="str">
         <v>绿色</v>
@@ -11183,7 +11363,7 @@
         <v>SLN1012</v>
       </c>
       <c r="C202" t="str">
-        <v>PITBULL 12 PL-77FV</v>
+        <v>PITBULL 12 PL-77FV | 1号</v>
       </c>
       <c r="D202" t="str">
         <v>绿色</v>
@@ -11227,7 +11407,7 @@
         <v>SLN1012</v>
       </c>
       <c r="C203" t="str">
-        <v>PITBULL 12 PL-77FV</v>
+        <v>PITBULL 12 PL-77FV | 1.2号</v>
       </c>
       <c r="D203" t="str">
         <v>绿色</v>
@@ -11271,7 +11451,7 @@
         <v>SLN1012</v>
       </c>
       <c r="C204" t="str">
-        <v>PITBULL 12 PL-77FV</v>
+        <v>PITBULL 12 PL-77FV | 1.5号</v>
       </c>
       <c r="D204" t="str">
         <v>绿色</v>
@@ -11315,7 +11495,7 @@
         <v>SLN1012</v>
       </c>
       <c r="C205" t="str">
-        <v>PITBULL 12 PL-77FV</v>
+        <v>PITBULL 12 PL-77FV | 2号</v>
       </c>
       <c r="D205" t="str">
         <v>绿色</v>
@@ -11403,7 +11583,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C207" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 0.8号</v>
       </c>
       <c r="D207" t="str">
         <v>绿色</v>
@@ -11447,7 +11627,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C208" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 1号</v>
       </c>
       <c r="D208" t="str">
         <v>绿色</v>
@@ -11491,7 +11671,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C209" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 1.2号</v>
       </c>
       <c r="D209" t="str">
         <v>绿色</v>
@@ -11535,7 +11715,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C210" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 1.5号</v>
       </c>
       <c r="D210" t="str">
         <v>绿色</v>
@@ -11579,7 +11759,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C211" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 2号</v>
       </c>
       <c r="D211" t="str">
         <v>绿色</v>
@@ -11623,7 +11803,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C212" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 3号</v>
       </c>
       <c r="D212" t="str">
         <v>绿色</v>
@@ -11667,7 +11847,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C213" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 4号</v>
       </c>
       <c r="D213" t="str">
         <v>绿色</v>
@@ -11711,7 +11891,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C214" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 5号</v>
       </c>
       <c r="D214" t="str">
         <v>绿色</v>
@@ -11755,7 +11935,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C215" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 6号</v>
       </c>
       <c r="D215" t="str">
         <v>绿色</v>
@@ -11799,7 +11979,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C216" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 0.6号</v>
       </c>
       <c r="D216" t="str">
         <v>灰色</v>
@@ -11843,7 +12023,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C217" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 0.8号 | 100m</v>
       </c>
       <c r="D217" t="str">
         <v>灰色</v>
@@ -11887,7 +12067,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C218" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 1号 | 100m</v>
       </c>
       <c r="D218" t="str">
         <v>灰色</v>
@@ -11931,7 +12111,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C219" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 1.2号 | 100m</v>
       </c>
       <c r="D219" t="str">
         <v>灰色</v>
@@ -11975,7 +12155,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C220" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 1.5号 | 100m</v>
       </c>
       <c r="D220" t="str">
         <v>灰色</v>
@@ -12019,7 +12199,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C221" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 2号 | 100m</v>
       </c>
       <c r="D221" t="str">
         <v>灰色</v>
@@ -12063,7 +12243,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C222" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 3号 | 100m</v>
       </c>
       <c r="D222" t="str">
         <v>灰色</v>
@@ -12107,7 +12287,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C223" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 4号 | 100m</v>
       </c>
       <c r="D223" t="str">
         <v>灰色</v>
@@ -12151,7 +12331,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C224" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 5号 | 100m</v>
       </c>
       <c r="D224" t="str">
         <v>灰色</v>
@@ -12195,7 +12375,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C225" t="str">
-        <v>HARDBULL 8+ LD-M48X</v>
+        <v>HARDBULL 8+ LD-M48X | 6号 | 100m</v>
       </c>
       <c r="D225" t="str">
         <v>灰色</v>
@@ -12283,7 +12463,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C227" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 0.8号</v>
       </c>
       <c r="D227" t="str">
         <v>绿色</v>
@@ -12327,7 +12507,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C228" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 1号</v>
       </c>
       <c r="D228" t="str">
         <v>绿色</v>
@@ -12371,7 +12551,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C229" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 1.2号</v>
       </c>
       <c r="D229" t="str">
         <v>绿色</v>
@@ -12415,7 +12595,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C230" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 1.5号</v>
       </c>
       <c r="D230" t="str">
         <v>绿色</v>
@@ -12459,7 +12639,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C231" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 2号</v>
       </c>
       <c r="D231" t="str">
         <v>绿色</v>
@@ -12503,7 +12683,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C232" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 3号</v>
       </c>
       <c r="D232" t="str">
         <v>绿色</v>
@@ -12547,7 +12727,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C233" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 4号</v>
       </c>
       <c r="D233" t="str">
         <v>绿色</v>
@@ -12591,7 +12771,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C234" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 5号</v>
       </c>
       <c r="D234" t="str">
         <v>绿色</v>
@@ -12635,7 +12815,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C235" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 6号</v>
       </c>
       <c r="D235" t="str">
         <v>绿色</v>
@@ -12679,7 +12859,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C236" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 0.6号</v>
       </c>
       <c r="D236" t="str">
         <v>灰色</v>
@@ -12723,7 +12903,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C237" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 0.8号 | 150m</v>
       </c>
       <c r="D237" t="str">
         <v>灰色</v>
@@ -12767,7 +12947,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C238" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 1号 | 150m</v>
       </c>
       <c r="D238" t="str">
         <v>灰色</v>
@@ -12811,7 +12991,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C239" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 1.2号 | 150m</v>
       </c>
       <c r="D239" t="str">
         <v>灰色</v>
@@ -12855,7 +13035,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C240" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 1.5号 | 150m</v>
       </c>
       <c r="D240" t="str">
         <v>灰色</v>
@@ -12899,7 +13079,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C241" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 2号 | 150m</v>
       </c>
       <c r="D241" t="str">
         <v>灰色</v>
@@ -12943,7 +13123,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C242" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 3号 | 150m</v>
       </c>
       <c r="D242" t="str">
         <v>灰色</v>
@@ -12987,7 +13167,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C243" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 4号 | 150m</v>
       </c>
       <c r="D243" t="str">
         <v>灰色</v>
@@ -13031,7 +13211,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C244" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 5号 | 150m</v>
       </c>
       <c r="D244" t="str">
         <v>灰色</v>
@@ -13075,7 +13255,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C245" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 6号 | 150m</v>
       </c>
       <c r="D245" t="str">
         <v>灰色</v>
@@ -13119,7 +13299,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C246" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 0.6号 | 150m</v>
       </c>
       <c r="D246" t="str">
         <v>10m x 5色</v>
@@ -13163,7 +13343,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C247" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 0.8号 | 150m | 19.5lb</v>
       </c>
       <c r="D247" t="str">
         <v>10m x 5色</v>
@@ -13207,7 +13387,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C248" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 1号 | 150m | 20.6lb</v>
       </c>
       <c r="D248" t="str">
         <v>10m x 5色</v>
@@ -13251,7 +13431,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C249" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 1.2号 | 150m | 23.4lb</v>
       </c>
       <c r="D249" t="str">
         <v>10m x 5色</v>
@@ -13295,7 +13475,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C250" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 1.5号 | 150m | 28.7lb</v>
       </c>
       <c r="D250" t="str">
         <v>10m x 5色</v>
@@ -13339,7 +13519,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C251" t="str">
-        <v>HARDBULL 8+ LD-M58X</v>
+        <v>HARDBULL 8+ LD-M58X | 2号 | 150m | 46.9lb</v>
       </c>
       <c r="D251" t="str">
         <v>10m x 5色</v>
@@ -13427,7 +13607,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C253" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 0.8号</v>
       </c>
       <c r="D253" t="str">
         <v>绿色</v>
@@ -13471,7 +13651,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C254" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 1号</v>
       </c>
       <c r="D254" t="str">
         <v>绿色</v>
@@ -13515,7 +13695,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C255" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 1.2号</v>
       </c>
       <c r="D255" t="str">
         <v>绿色</v>
@@ -13559,7 +13739,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C256" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 1.5号</v>
       </c>
       <c r="D256" t="str">
         <v>绿色</v>
@@ -13603,7 +13783,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C257" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 2号</v>
       </c>
       <c r="D257" t="str">
         <v>绿色</v>
@@ -13647,7 +13827,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C258" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 3号</v>
       </c>
       <c r="D258" t="str">
         <v>绿色</v>
@@ -13691,7 +13871,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C259" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 4号</v>
       </c>
       <c r="D259" t="str">
         <v>绿色</v>
@@ -13735,7 +13915,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C260" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 5号</v>
       </c>
       <c r="D260" t="str">
         <v>绿色</v>
@@ -13779,7 +13959,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C261" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 6号</v>
       </c>
       <c r="D261" t="str">
         <v>绿色</v>
@@ -13823,7 +14003,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C262" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 0.6号</v>
       </c>
       <c r="D262" t="str">
         <v>灰色</v>
@@ -13867,7 +14047,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C263" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 0.8号 | 200m</v>
       </c>
       <c r="D263" t="str">
         <v>灰色</v>
@@ -13911,7 +14091,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C264" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 1号 | 200m</v>
       </c>
       <c r="D264" t="str">
         <v>灰色</v>
@@ -13955,7 +14135,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C265" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 1.2号 | 200m</v>
       </c>
       <c r="D265" t="str">
         <v>灰色</v>
@@ -13999,7 +14179,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C266" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 1.5号 | 200m</v>
       </c>
       <c r="D266" t="str">
         <v>灰色</v>
@@ -14043,7 +14223,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C267" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 2号 | 200m</v>
       </c>
       <c r="D267" t="str">
         <v>灰色</v>
@@ -14087,7 +14267,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C268" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 3号 | 200m</v>
       </c>
       <c r="D268" t="str">
         <v>灰色</v>
@@ -14131,7 +14311,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C269" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 4号 | 200m</v>
       </c>
       <c r="D269" t="str">
         <v>灰色</v>
@@ -14175,7 +14355,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C270" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 5号 | 200m</v>
       </c>
       <c r="D270" t="str">
         <v>灰色</v>
@@ -14219,7 +14399,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C271" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 6号 | 200m</v>
       </c>
       <c r="D271" t="str">
         <v>灰色</v>
@@ -14263,7 +14443,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C272" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 0.6号 | 200m</v>
       </c>
       <c r="D272" t="str">
         <v>10m x 5色</v>
@@ -14307,7 +14487,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C273" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 0.8号 | 200m | 19.5lb</v>
       </c>
       <c r="D273" t="str">
         <v>10m x 5色</v>
@@ -14351,7 +14531,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C274" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 1号 | 200m | 20.6lb</v>
       </c>
       <c r="D274" t="str">
         <v>10m x 5色</v>
@@ -14395,7 +14575,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C275" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 1.2号 | 200m | 23.4lb</v>
       </c>
       <c r="D275" t="str">
         <v>10m x 5色</v>
@@ -14439,7 +14619,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C276" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 1.5号 | 200m | 28.7lb</v>
       </c>
       <c r="D276" t="str">
         <v>10m x 5色</v>
@@ -14483,7 +14663,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C277" t="str">
-        <v>HARDBULL 8+ LD-M68X</v>
+        <v>HARDBULL 8+ LD-M68X | 2号 | 200m | 46.9lb</v>
       </c>
       <c r="D277" t="str">
         <v>10m x 5色</v>
@@ -14571,7 +14751,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C279" t="str">
-        <v>HARDBULL 8+ LD-M78Y</v>
+        <v>HARDBULL 8+ LD-M78Y | 0.8号</v>
       </c>
       <c r="D279" t="str">
         <v>10m x 5色</v>
@@ -14615,7 +14795,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C280" t="str">
-        <v>HARDBULL 8+ LD-M78Y</v>
+        <v>HARDBULL 8+ LD-M78Y | 1号</v>
       </c>
       <c r="D280" t="str">
         <v>10m x 5色</v>
@@ -14659,7 +14839,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C281" t="str">
-        <v>HARDBULL 8+ LD-M78Y</v>
+        <v>HARDBULL 8+ LD-M78Y | 1.2号</v>
       </c>
       <c r="D281" t="str">
         <v>10m x 5色</v>
@@ -14703,7 +14883,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C282" t="str">
-        <v>HARDBULL 8+ LD-M78Y</v>
+        <v>HARDBULL 8+ LD-M78Y | 1.5号</v>
       </c>
       <c r="D282" t="str">
         <v>10m x 5色</v>
@@ -14747,7 +14927,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C283" t="str">
-        <v>HARDBULL 8+ LD-M78Y</v>
+        <v>HARDBULL 8+ LD-M78Y | 2号</v>
       </c>
       <c r="D283" t="str">
         <v>10m x 5色</v>
@@ -14791,7 +14971,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C284" t="str">
-        <v>HARDBULL 8+ LD-M78Y</v>
+        <v>HARDBULL 8+ LD-M78Y | 3号</v>
       </c>
       <c r="D284" t="str">
         <v>10m x 5色</v>
@@ -14835,7 +15015,7 @@
         <v>SLN1013</v>
       </c>
       <c r="C285" t="str">
-        <v>HARDBULL 8+ LD-M78Y</v>
+        <v>HARDBULL 8+ LD-M78Y | 4号</v>
       </c>
       <c r="D285" t="str">
         <v>10m x 5色</v>
@@ -14923,7 +15103,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C287" t="str">
-        <v>GRAPPLER 8 LD-A61U</v>
+        <v>GRAPPLER 8 LD-A61U | 1号</v>
       </c>
       <c r="D287" t="str">
         <v>5色</v>
@@ -14967,7 +15147,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C288" t="str">
-        <v>GRAPPLER 8 LD-A61U</v>
+        <v>GRAPPLER 8 LD-A61U | 1.2号</v>
       </c>
       <c r="D288" t="str">
         <v>5色</v>
@@ -15011,7 +15191,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C289" t="str">
-        <v>GRAPPLER 8 LD-A61U</v>
+        <v>GRAPPLER 8 LD-A61U | 1.5号</v>
       </c>
       <c r="D289" t="str">
         <v>5色</v>
@@ -15055,7 +15235,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C290" t="str">
-        <v>GRAPPLER 8 LD-A61U</v>
+        <v>GRAPPLER 8 LD-A61U | 2号</v>
       </c>
       <c r="D290" t="str">
         <v>5色</v>
@@ -15099,7 +15279,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C291" t="str">
-        <v>GRAPPLER 8 LD-A61U</v>
+        <v>GRAPPLER 8 LD-A61U | 3号</v>
       </c>
       <c r="D291" t="str">
         <v>5色</v>
@@ -15187,7 +15367,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C293" t="str">
-        <v>GRAPPLER 8 LD-A71U</v>
+        <v>GRAPPLER 8 LD-A71U | 1号</v>
       </c>
       <c r="D293" t="str">
         <v>5色</v>
@@ -15231,7 +15411,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C294" t="str">
-        <v>GRAPPLER 8 LD-A71U</v>
+        <v>GRAPPLER 8 LD-A71U | 1.2号</v>
       </c>
       <c r="D294" t="str">
         <v>5色</v>
@@ -15275,7 +15455,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C295" t="str">
-        <v>GRAPPLER 8 LD-A71U</v>
+        <v>GRAPPLER 8 LD-A71U | 1.5号</v>
       </c>
       <c r="D295" t="str">
         <v>5色</v>
@@ -15319,7 +15499,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C296" t="str">
-        <v>GRAPPLER 8 LD-A71U</v>
+        <v>GRAPPLER 8 LD-A71U | 2号</v>
       </c>
       <c r="D296" t="str">
         <v>5色</v>
@@ -15363,7 +15543,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C297" t="str">
-        <v>GRAPPLER 8 LD-A71U</v>
+        <v>GRAPPLER 8 LD-A71U | 3号</v>
       </c>
       <c r="D297" t="str">
         <v>5色</v>
@@ -15407,7 +15587,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C298" t="str">
-        <v>GRAPPLER 8 LD-A71U</v>
+        <v>GRAPPLER 8 LD-A71U | 4号</v>
       </c>
       <c r="D298" t="str">
         <v>5色</v>
@@ -15451,7 +15631,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C299" t="str">
-        <v>GRAPPLER 8 LD-A71U</v>
+        <v>GRAPPLER 8 LD-A71U | 5号</v>
       </c>
       <c r="D299" t="str">
         <v>5色</v>
@@ -15495,7 +15675,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C300" t="str">
-        <v>GRAPPLER 8 LD-A71U</v>
+        <v>GRAPPLER 8 LD-A71U | 6号</v>
       </c>
       <c r="D300" t="str">
         <v>5色</v>
@@ -15539,7 +15719,7 @@
         <v>SLN1014</v>
       </c>
       <c r="C301" t="str">
-        <v>GRAPPLER 8 LD-A71U</v>
+        <v>GRAPPLER 8 LD-A71U | 8号</v>
       </c>
       <c r="D301" t="str">
         <v>5色</v>
@@ -15671,7 +15851,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C304" t="str">
-        <v>Tanatoru 4 PL-F54R</v>
+        <v>Tanatoru 4 PL-F54R | 1号</v>
       </c>
       <c r="D304" t="str">
         <v>5色</v>
@@ -15715,7 +15895,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C305" t="str">
-        <v>Tanatoru 4 PL-F54R</v>
+        <v>Tanatoru 4 PL-F54R | 1.5号</v>
       </c>
       <c r="D305" t="str">
         <v>5色</v>
@@ -15759,7 +15939,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C306" t="str">
-        <v>Tanatoru 4 PL-F54R</v>
+        <v>Tanatoru 4 PL-F54R | 2号</v>
       </c>
       <c r="D306" t="str">
         <v>5色</v>
@@ -15847,7 +16027,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C308" t="str">
-        <v>Tanatoru 4 PL-F64R</v>
+        <v>Tanatoru 4 PL-F64R | 0.8号</v>
       </c>
       <c r="D308" t="str">
         <v>5色</v>
@@ -15891,7 +16071,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C309" t="str">
-        <v>Tanatoru 4 PL-F64R</v>
+        <v>Tanatoru 4 PL-F64R | 1号</v>
       </c>
       <c r="D309" t="str">
         <v>5色</v>
@@ -15935,7 +16115,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C310" t="str">
-        <v>Tanatoru 4 PL-F64R</v>
+        <v>Tanatoru 4 PL-F64R | 1.5号</v>
       </c>
       <c r="D310" t="str">
         <v>5色</v>
@@ -15979,7 +16159,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C311" t="str">
-        <v>Tanatoru 4 PL-F64R</v>
+        <v>Tanatoru 4 PL-F64R | 2号</v>
       </c>
       <c r="D311" t="str">
         <v>5色</v>
@@ -16023,7 +16203,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C312" t="str">
-        <v>Tanatoru 4 PL-F64R</v>
+        <v>Tanatoru 4 PL-F64R | 3号</v>
       </c>
       <c r="D312" t="str">
         <v>5色</v>
@@ -16111,7 +16291,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C314" t="str">
-        <v>Tanatoru 4 PL-F74R</v>
+        <v>Tanatoru 4 PL-F74R | 0.8号</v>
       </c>
       <c r="D314" t="str">
         <v>5色</v>
@@ -16155,7 +16335,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C315" t="str">
-        <v>Tanatoru 4 PL-F74R</v>
+        <v>Tanatoru 4 PL-F74R | 1号</v>
       </c>
       <c r="D315" t="str">
         <v>5色</v>
@@ -16199,7 +16379,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C316" t="str">
-        <v>Tanatoru 4 PL-F74R</v>
+        <v>Tanatoru 4 PL-F74R | 1.5号</v>
       </c>
       <c r="D316" t="str">
         <v>5色</v>
@@ -16243,7 +16423,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C317" t="str">
-        <v>Tanatoru 4 PL-F74R</v>
+        <v>Tanatoru 4 PL-F74R | 2号</v>
       </c>
       <c r="D317" t="str">
         <v>5色</v>
@@ -16287,7 +16467,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C318" t="str">
-        <v>Tanatoru 4 PL-F74R</v>
+        <v>Tanatoru 4 PL-F74R | 3号</v>
       </c>
       <c r="D318" t="str">
         <v>5色</v>
@@ -16331,7 +16511,7 @@
         <v>SLN1016</v>
       </c>
       <c r="C319" t="str">
-        <v>Tanatoru 4 PL-F74R</v>
+        <v>Tanatoru 4 PL-F74R | 4号</v>
       </c>
       <c r="D319" t="str">
         <v>5色</v>
@@ -16463,7 +16643,7 @@
         <v>SLN1017</v>
       </c>
       <c r="C322" t="str">
-        <v>KAIKON LA-C70V</v>
+        <v>KAIKON LA-C70V | 20号</v>
       </c>
       <c r="D322" t="str">
         <v>棕色</v>
@@ -16507,7 +16687,7 @@
         <v>SLN1017</v>
       </c>
       <c r="C323" t="str">
-        <v>KAIKON LA-C70V</v>
+        <v>KAIKON LA-C70V | 22号</v>
       </c>
       <c r="D323" t="str">
         <v>棕色</v>
@@ -16551,7 +16731,7 @@
         <v>SLN1017</v>
       </c>
       <c r="C324" t="str">
-        <v>KAIKON LA-C70V</v>
+        <v>KAIKON LA-C70V | 24号</v>
       </c>
       <c r="D324" t="str">
         <v>棕色</v>
@@ -16639,7 +16819,7 @@
         <v>SLN1018</v>
       </c>
       <c r="C326" t="str">
-        <v>BULL'S EYE 远投 LA-C61V</v>
+        <v>BULL'S EYE 远投 LA-C61V | 200m</v>
       </c>
       <c r="D326" t="str">
         <v>荧光绿</v>
@@ -16683,7 +16863,7 @@
         <v>SLN1018</v>
       </c>
       <c r="C327" t="str">
-        <v>BULL'S EYE 远投 LA-C61V</v>
+        <v>BULL'S EYE 远投 LA-C61V | 200m | 828804</v>
       </c>
       <c r="D327" t="str">
         <v>荧光绿</v>
@@ -16727,7 +16907,7 @@
         <v>SLN1018</v>
       </c>
       <c r="C328" t="str">
-        <v>BULL'S EYE 远投 LA-C61V</v>
+        <v>BULL'S EYE 远投 LA-C61V | 200m | 828811</v>
       </c>
       <c r="D328" t="str">
         <v>荧光绿</v>
@@ -16771,7 +16951,7 @@
         <v>SLN1018</v>
       </c>
       <c r="C329" t="str">
-        <v>BULL'S EYE 远投 LA-C61V</v>
+        <v>BULL'S EYE 远投 LA-C61V | 200m | 828828</v>
       </c>
       <c r="D329" t="str">
         <v>荧光绿</v>
@@ -16859,7 +17039,7 @@
         <v>SLN1019</v>
       </c>
       <c r="C331" t="str">
-        <v>OCEA JIGGER MASTER 前导线 CL-O36P</v>
+        <v>OCEA JIGGER MASTER 前导线 CL-O36P | 5号</v>
       </c>
       <c r="D331" t="str">
         <v>透明色</v>
@@ -16903,7 +17083,7 @@
         <v>SLN1019</v>
       </c>
       <c r="C332" t="str">
-        <v>OCEA JIGGER MASTER 前导线 CL-O36P</v>
+        <v>OCEA JIGGER MASTER 前导线 CL-O36P | 6号</v>
       </c>
       <c r="D332" t="str">
         <v>透明色</v>
@@ -16947,7 +17127,7 @@
         <v>SLN1019</v>
       </c>
       <c r="C333" t="str">
-        <v>OCEA JIGGER MASTER 前导线 CL-O36P</v>
+        <v>OCEA JIGGER MASTER 前导线 CL-O36P | 8号</v>
       </c>
       <c r="D333" t="str">
         <v>透明色</v>
@@ -16991,7 +17171,7 @@
         <v>SLN1019</v>
       </c>
       <c r="C334" t="str">
-        <v>OCEA JIGGER MASTER 前导线 CL-O36P</v>
+        <v>OCEA JIGGER MASTER 前导线 CL-O36P | 12号</v>
       </c>
       <c r="D334" t="str">
         <v>透明色</v>
@@ -17035,7 +17215,7 @@
         <v>SLN1019</v>
       </c>
       <c r="C335" t="str">
-        <v>OCEA JIGGER MASTER 前导线 CL-O36P</v>
+        <v>OCEA JIGGER MASTER 前导线 CL-O36P | 14号</v>
       </c>
       <c r="D335" t="str">
         <v>透明色</v>
@@ -17079,7 +17259,7 @@
         <v>SLN1019</v>
       </c>
       <c r="C336" t="str">
-        <v>OCEA JIGGER MASTER 前导线 CL-O36P</v>
+        <v>OCEA JIGGER MASTER 前导线 CL-O36P | 18号</v>
       </c>
       <c r="D336" t="str">
         <v>透明色</v>
@@ -17167,7 +17347,7 @@
         <v>SLN1020</v>
       </c>
       <c r="C338" t="str">
-        <v>Sephia 8+ LD-E51T</v>
+        <v>Sephia 8+ LD-E51T | 0.5号</v>
       </c>
       <c r="D338" t="str">
         <v>5色</v>
@@ -17211,7 +17391,7 @@
         <v>SLN1020</v>
       </c>
       <c r="C339" t="str">
-        <v>Sephia 8+ LD-E51T</v>
+        <v>Sephia 8+ LD-E51T | 0.6号</v>
       </c>
       <c r="D339" t="str">
         <v>5色</v>
@@ -17255,7 +17435,7 @@
         <v>SLN1020</v>
       </c>
       <c r="C340" t="str">
-        <v>Sephia 8+ LD-E51T</v>
+        <v>Sephia 8+ LD-E51T | 0.8号</v>
       </c>
       <c r="D340" t="str">
         <v>5色</v>
@@ -17343,7 +17523,7 @@
         <v>SLN1020</v>
       </c>
       <c r="C342" t="str">
-        <v>Sephia 8+ LD-E61T</v>
+        <v>Sephia 8+ LD-E61T | 0.5号</v>
       </c>
       <c r="D342" t="str">
         <v>5色</v>
@@ -17387,7 +17567,7 @@
         <v>SLN1020</v>
       </c>
       <c r="C343" t="str">
-        <v>Sephia 8+ LD-E61T</v>
+        <v>Sephia 8+ LD-E61T | 0.6号</v>
       </c>
       <c r="D343" t="str">
         <v>5色</v>
@@ -17431,7 +17611,7 @@
         <v>SLN1020</v>
       </c>
       <c r="C344" t="str">
-        <v>Sephia 8+ LD-E61T</v>
+        <v>Sephia 8+ LD-E61T | 0.8号</v>
       </c>
       <c r="D344" t="str">
         <v>5色</v>
@@ -17519,7 +17699,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C346" t="str">
-        <v>PITBULL 8+ LD-M51T</v>
+        <v>PITBULL 8+ LD-M51T | 0.5号</v>
       </c>
       <c r="D346" t="str">
         <v>粉色</v>
@@ -17563,7 +17743,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C347" t="str">
-        <v>PITBULL 8+ LD-M51T</v>
+        <v>PITBULL 8+ LD-M51T | 0.6号</v>
       </c>
       <c r="D347" t="str">
         <v>粉色</v>
@@ -17607,7 +17787,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C348" t="str">
-        <v>PITBULL 8+ LD-M51T</v>
+        <v>PITBULL 8+ LD-M51T | 0.8号</v>
       </c>
       <c r="D348" t="str">
         <v>粉色</v>
@@ -17651,7 +17831,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C349" t="str">
-        <v>PITBULL 8+ LD-M51T</v>
+        <v>PITBULL 8+ LD-M51T | 1号</v>
       </c>
       <c r="D349" t="str">
         <v>粉色</v>
@@ -17695,7 +17875,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C350" t="str">
-        <v>PITBULL 8+ LD-M51T</v>
+        <v>PITBULL 8+ LD-M51T | 1.2号</v>
       </c>
       <c r="D350" t="str">
         <v>粉色</v>
@@ -17739,7 +17919,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C351" t="str">
-        <v>PITBULL 8+ LD-M51T</v>
+        <v>PITBULL 8+ LD-M51T | 1.5号</v>
       </c>
       <c r="D351" t="str">
         <v>粉色</v>
@@ -17783,7 +17963,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C352" t="str">
-        <v>PITBULL 8+ LD-M51T</v>
+        <v>PITBULL 8+ LD-M51T | 2号</v>
       </c>
       <c r="D352" t="str">
         <v>粉色</v>
@@ -17871,7 +18051,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C354" t="str">
-        <v>PITBULL 8+ LD-M61T</v>
+        <v>PITBULL 8+ LD-M61T | 0.5号</v>
       </c>
       <c r="D354" t="str">
         <v>粉色</v>
@@ -17915,7 +18095,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C355" t="str">
-        <v>PITBULL 8+ LD-M61T</v>
+        <v>PITBULL 8+ LD-M61T | 0.6号</v>
       </c>
       <c r="D355" t="str">
         <v>粉色</v>
@@ -17959,7 +18139,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C356" t="str">
-        <v>PITBULL 8+ LD-M61T</v>
+        <v>PITBULL 8+ LD-M61T | 0.8号</v>
       </c>
       <c r="D356" t="str">
         <v>粉色</v>
@@ -18003,7 +18183,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C357" t="str">
-        <v>PITBULL 8+ LD-M61T</v>
+        <v>PITBULL 8+ LD-M61T | 1号</v>
       </c>
       <c r="D357" t="str">
         <v>粉色</v>
@@ -18047,7 +18227,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C358" t="str">
-        <v>PITBULL 8+ LD-M61T</v>
+        <v>PITBULL 8+ LD-M61T | 1.2号</v>
       </c>
       <c r="D358" t="str">
         <v>粉色</v>
@@ -18091,7 +18271,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C359" t="str">
-        <v>PITBULL 8+ LD-M61T</v>
+        <v>PITBULL 8+ LD-M61T | 1.5号</v>
       </c>
       <c r="D359" t="str">
         <v>粉色</v>
@@ -18135,7 +18315,7 @@
         <v>SLN1021</v>
       </c>
       <c r="C360" t="str">
-        <v>PITBULL 8+ LD-M61T</v>
+        <v>PITBULL 8+ LD-M61T | 2号</v>
       </c>
       <c r="D360" t="str">
         <v>粉色</v>
@@ -18223,7 +18403,7 @@
         <v>SLN1022</v>
       </c>
       <c r="C362" t="str">
-        <v>FUKASE 船 LB-F70Y</v>
+        <v>FUKASE 船 LB-F70Y | 6号</v>
       </c>
       <c r="D362" t="str">
         <v>粉色</v>
@@ -18267,7 +18447,7 @@
         <v>SLN1022</v>
       </c>
       <c r="C363" t="str">
-        <v>FUKASE 船 LB-F70Y</v>
+        <v>FUKASE 船 LB-F70Y | 7号</v>
       </c>
       <c r="D363" t="str">
         <v>粉色</v>
@@ -18311,7 +18491,7 @@
         <v>SLN1022</v>
       </c>
       <c r="C364" t="str">
-        <v>FUKASE 船 LB-F70Y</v>
+        <v>FUKASE 船 LB-F70Y | 8号</v>
       </c>
       <c r="D364" t="str">
         <v>粉色</v>
@@ -18399,7 +18579,7 @@
         <v>SLN1023</v>
       </c>
       <c r="C366" t="str">
-        <v>Sephia G5 PL-E55N</v>
+        <v>Sephia G5 PL-E55N | 150m</v>
       </c>
       <c r="D366" t="str">
         <v>5色</v>
@@ -18443,7 +18623,7 @@
         <v>SLN1023</v>
       </c>
       <c r="C367" t="str">
-        <v>Sephia G5 PL-E55N</v>
+        <v>Sephia G5 PL-E55N | 150m | 442697</v>
       </c>
       <c r="D367" t="str">
         <v>5色</v>
@@ -18487,7 +18667,7 @@
         <v>SLN1023</v>
       </c>
       <c r="C368" t="str">
-        <v>Sephia G5 PL-E55N</v>
+        <v>Sephia G5 PL-E55N | 150m | 442703</v>
       </c>
       <c r="D368" t="str">
         <v>5色</v>
@@ -18575,7 +18755,7 @@
         <v>SLN1023</v>
       </c>
       <c r="C370" t="str">
-        <v>Sephia G5 PL-E65N</v>
+        <v>Sephia G5 PL-E65N | 200m</v>
       </c>
       <c r="D370" t="str">
         <v>5色</v>
@@ -18619,7 +18799,7 @@
         <v>SLN1023</v>
       </c>
       <c r="C371" t="str">
-        <v>Sephia G5 PL-E65N</v>
+        <v>Sephia G5 PL-E65N | 200m | 442734</v>
       </c>
       <c r="D371" t="str">
         <v>5色</v>
@@ -18707,7 +18887,7 @@
         <v>SLN1024</v>
       </c>
       <c r="C373" t="str">
-        <v>Sephia 8 LD-E51W</v>
+        <v>Sephia 8 LD-E51W | 0.5号</v>
       </c>
       <c r="D373" t="str">
         <v>10m x 5色</v>
@@ -18751,7 +18931,7 @@
         <v>SLN1024</v>
       </c>
       <c r="C374" t="str">
-        <v>Sephia 8 LD-E51W</v>
+        <v>Sephia 8 LD-E51W | 0.6号</v>
       </c>
       <c r="D374" t="str">
         <v>10m x 5色</v>
@@ -18795,7 +18975,7 @@
         <v>SLN1024</v>
       </c>
       <c r="C375" t="str">
-        <v>Sephia 8 LD-E51W</v>
+        <v>Sephia 8 LD-E51W | 0.8号</v>
       </c>
       <c r="D375" t="str">
         <v>10m x 5色</v>
@@ -18883,7 +19063,7 @@
         <v>SLN1024</v>
       </c>
       <c r="C377" t="str">
-        <v>Sephia 8 LD-E61W</v>
+        <v>Sephia 8 LD-E61W | 0.5号</v>
       </c>
       <c r="D377" t="str">
         <v>10m x 5色</v>
@@ -18927,7 +19107,7 @@
         <v>SLN1024</v>
       </c>
       <c r="C378" t="str">
-        <v>Sephia 8 LD-E61W</v>
+        <v>Sephia 8 LD-E61W | 0.6号</v>
       </c>
       <c r="D378" t="str">
         <v>10m x 5色</v>
@@ -18971,7 +19151,7 @@
         <v>SLN1024</v>
       </c>
       <c r="C379" t="str">
-        <v>Sephia 8 LD-E61W</v>
+        <v>Sephia 8 LD-E61W | 0.8号</v>
       </c>
       <c r="D379" t="str">
         <v>10m x 5色</v>
@@ -19059,7 +19239,7 @@
         <v>SLN1025</v>
       </c>
       <c r="C381" t="str">
-        <v>SPINPOWER EX4 PL-N14P</v>
+        <v>SPINPOWER EX4 PL-N14P | 12m</v>
       </c>
       <c r="D381" t="str">
         <v>黑色</v>
@@ -19103,7 +19283,7 @@
         <v>SLN1025</v>
       </c>
       <c r="C382" t="str">
-        <v>SPINPOWER EX4 PL-N14P</v>
+        <v>SPINPOWER EX4 PL-N14P | 12m | 463555</v>
       </c>
       <c r="D382" t="str">
         <v>黑色</v>
@@ -19191,7 +19371,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C384" t="str">
-        <v>GRAPPLER 4 LD-A62W</v>
+        <v>GRAPPLER 4 LD-A62W | 1号</v>
       </c>
       <c r="D384" t="str">
         <v/>
@@ -19235,7 +19415,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C385" t="str">
-        <v>GRAPPLER 4 LD-A62W</v>
+        <v>GRAPPLER 4 LD-A62W | 1.2号</v>
       </c>
       <c r="D385" t="str">
         <v/>
@@ -19279,7 +19459,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C386" t="str">
-        <v>GRAPPLER 4 LD-A62W</v>
+        <v>GRAPPLER 4 LD-A62W | 1.5号</v>
       </c>
       <c r="D386" t="str">
         <v/>
@@ -19323,7 +19503,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C387" t="str">
-        <v>GRAPPLER 4 LD-A62W</v>
+        <v>GRAPPLER 4 LD-A62W | 2号</v>
       </c>
       <c r="D387" t="str">
         <v/>
@@ -19367,7 +19547,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C388" t="str">
-        <v>GRAPPLER 4 LD-A62W</v>
+        <v>GRAPPLER 4 LD-A62W | 3号</v>
       </c>
       <c r="D388" t="str">
         <v/>
@@ -19455,7 +19635,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C390" t="str">
-        <v>GRAPPLER 4 LD-A72W</v>
+        <v>GRAPPLER 4 LD-A72W | 1号</v>
       </c>
       <c r="D390" t="str">
         <v/>
@@ -19499,7 +19679,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C391" t="str">
-        <v>GRAPPLER 4 LD-A72W</v>
+        <v>GRAPPLER 4 LD-A72W | 1.2号</v>
       </c>
       <c r="D391" t="str">
         <v/>
@@ -19543,7 +19723,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C392" t="str">
-        <v>GRAPPLER 4 LD-A72W</v>
+        <v>GRAPPLER 4 LD-A72W | 1.5号</v>
       </c>
       <c r="D392" t="str">
         <v/>
@@ -19587,7 +19767,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C393" t="str">
-        <v>GRAPPLER 4 LD-A72W</v>
+        <v>GRAPPLER 4 LD-A72W | 2号</v>
       </c>
       <c r="D393" t="str">
         <v/>
@@ -19631,7 +19811,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C394" t="str">
-        <v>GRAPPLER 4 LD-A72W</v>
+        <v>GRAPPLER 4 LD-A72W | 3号</v>
       </c>
       <c r="D394" t="str">
         <v/>
@@ -19675,7 +19855,7 @@
         <v>SLN1026</v>
       </c>
       <c r="C395" t="str">
-        <v>GRAPPLER 4 LD-A72W</v>
+        <v>GRAPPLER 4 LD-A72W | 4号</v>
       </c>
       <c r="D395" t="str">
         <v/>
@@ -19763,7 +19943,7 @@
         <v>SLN1027</v>
       </c>
       <c r="C397" t="str">
-        <v>LAKEMASTER LD-W21S</v>
+        <v>LAKEMASTER LD-W21S | 0.25号</v>
       </c>
       <c r="D397" t="str">
         <v>白色</v>
@@ -19807,7 +19987,7 @@
         <v>SLN1027</v>
       </c>
       <c r="C398" t="str">
-        <v>LAKEMASTER LD-W21S</v>
+        <v>LAKEMASTER LD-W21S | 0.3号</v>
       </c>
       <c r="D398" t="str">
         <v>白色</v>
@@ -19895,7 +20075,7 @@
         <v>SLN1027</v>
       </c>
       <c r="C400" t="str">
-        <v>LAKEMASTER LD-W41S</v>
+        <v>LAKEMASTER LD-W41S | 0.25号</v>
       </c>
       <c r="D400" t="str">
         <v>白色</v>
@@ -19939,7 +20119,7 @@
         <v>SLN1027</v>
       </c>
       <c r="C401" t="str">
-        <v>LAKEMASTER LD-W41S</v>
+        <v>LAKEMASTER LD-W41S | 0.3号</v>
       </c>
       <c r="D401" t="str">
         <v>白色</v>
@@ -20027,7 +20207,7 @@
         <v>SLN1028</v>
       </c>
       <c r="C403" t="str">
-        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q</v>
+        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q | 1.5号</v>
       </c>
       <c r="D403" t="str">
         <v>灰色</v>
@@ -20071,7 +20251,7 @@
         <v>SLN1028</v>
       </c>
       <c r="C404" t="str">
-        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q</v>
+        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q | 1.7号</v>
       </c>
       <c r="D404" t="str">
         <v>灰色</v>
@@ -20115,7 +20295,7 @@
         <v>SLN1028</v>
       </c>
       <c r="C405" t="str">
-        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q</v>
+        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q | 2号</v>
       </c>
       <c r="D405" t="str">
         <v>灰色</v>
@@ -20159,7 +20339,7 @@
         <v>SLN1028</v>
       </c>
       <c r="C406" t="str">
-        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q</v>
+        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q | 2.5号</v>
       </c>
       <c r="D406" t="str">
         <v>灰色</v>
@@ -20203,7 +20383,7 @@
         <v>SLN1028</v>
       </c>
       <c r="C407" t="str">
-        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q</v>
+        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q | 3号</v>
       </c>
       <c r="D407" t="str">
         <v>灰色</v>
@@ -20247,7 +20427,7 @@
         <v>SLN1028</v>
       </c>
       <c r="C408" t="str">
-        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q</v>
+        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q | 4号</v>
       </c>
       <c r="D408" t="str">
         <v>灰色</v>
@@ -20291,7 +20471,7 @@
         <v>SLN1028</v>
       </c>
       <c r="C409" t="str">
-        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q</v>
+        <v>LIMITED PRO MASTER TOUGH-MUD CL-I34Q | 5号</v>
       </c>
       <c r="D409" t="str">
         <v>灰色</v>
@@ -20379,7 +20559,7 @@
         <v>SLN1029</v>
       </c>
       <c r="C411" t="str">
-        <v>LIMITED PRO MASTER LB-C31U</v>
+        <v>LIMITED PRO MASTER LB-C31U | 1号</v>
       </c>
       <c r="D411" t="str">
         <v>透明色</v>
@@ -20423,7 +20603,7 @@
         <v>SLN1029</v>
       </c>
       <c r="C412" t="str">
-        <v>LIMITED PRO MASTER LB-C31U</v>
+        <v>LIMITED PRO MASTER LB-C31U | 1.2号</v>
       </c>
       <c r="D412" t="str">
         <v>透明色</v>
@@ -20467,7 +20647,7 @@
         <v>SLN1029</v>
       </c>
       <c r="C413" t="str">
-        <v>LIMITED PRO MASTER LB-C31U</v>
+        <v>LIMITED PRO MASTER LB-C31U | 1.5号</v>
       </c>
       <c r="D413" t="str">
         <v>透明色</v>
@@ -20511,7 +20691,7 @@
         <v>SLN1029</v>
       </c>
       <c r="C414" t="str">
-        <v>LIMITED PRO MASTER LB-C31U</v>
+        <v>LIMITED PRO MASTER LB-C31U | 1.75号</v>
       </c>
       <c r="D414" t="str">
         <v>透明色</v>
@@ -20555,7 +20735,7 @@
         <v>SLN1029</v>
       </c>
       <c r="C415" t="str">
-        <v>LIMITED PRO MASTER LB-C31U</v>
+        <v>LIMITED PRO MASTER LB-C31U | 2号</v>
       </c>
       <c r="D415" t="str">
         <v>透明色</v>
@@ -20599,7 +20779,7 @@
         <v>SLN1029</v>
       </c>
       <c r="C416" t="str">
-        <v>LIMITED PRO MASTER LB-C31U</v>
+        <v>LIMITED PRO MASTER LB-C31U | 2.5号</v>
       </c>
       <c r="D416" t="str">
         <v>透明色</v>
@@ -20643,7 +20823,7 @@
         <v>SLN1029</v>
       </c>
       <c r="C417" t="str">
-        <v>LIMITED PRO MASTER LB-C31U</v>
+        <v>LIMITED PRO MASTER LB-C31U | 3号</v>
       </c>
       <c r="D417" t="str">
         <v>透明色</v>
@@ -20731,7 +20911,7 @@
         <v>SLN1029</v>
       </c>
       <c r="C419" t="str">
-        <v>LIMITED PRO MASTER LB-C32U</v>
+        <v>LIMITED PRO MASTER LB-C32U | 5号</v>
       </c>
       <c r="D419" t="str">
         <v>透明色</v>
@@ -20775,7 +20955,7 @@
         <v>SLN1029</v>
       </c>
       <c r="C420" t="str">
-        <v>LIMITED PRO MASTER LB-C32U</v>
+        <v>LIMITED PRO MASTER LB-C32U | 6号</v>
       </c>
       <c r="D420" t="str">
         <v>透明色</v>
@@ -20863,7 +21043,7 @@
         <v>SLN1030</v>
       </c>
       <c r="C422" t="str">
-        <v>BB-X HYPER-REPEL α 漂浮 NL-I51Q</v>
+        <v>BB-X HYPER-REPEL α 漂浮 NL-I51Q | 2号</v>
       </c>
       <c r="D422" t="str">
         <v>白色</v>
@@ -20907,7 +21087,7 @@
         <v>SLN1030</v>
       </c>
       <c r="C423" t="str">
-        <v>BB-X HYPER-REPEL α 漂浮 NL-I51Q</v>
+        <v>BB-X HYPER-REPEL α 漂浮 NL-I51Q | 2.5号</v>
       </c>
       <c r="D423" t="str">
         <v>白色</v>
@@ -20951,7 +21131,7 @@
         <v>SLN1030</v>
       </c>
       <c r="C424" t="str">
-        <v>BB-X HYPER-REPEL α 漂浮 NL-I51Q</v>
+        <v>BB-X HYPER-REPEL α 漂浮 NL-I51Q | 3号</v>
       </c>
       <c r="D424" t="str">
         <v>白色</v>
@@ -20995,7 +21175,7 @@
         <v>SLN1030</v>
       </c>
       <c r="C425" t="str">
-        <v>BB-X HYPER-REPEL α 漂浮 NL-I51Q</v>
+        <v>BB-X HYPER-REPEL α 漂浮 NL-I51Q | 4号</v>
       </c>
       <c r="D425" t="str">
         <v>白色</v>
@@ -21083,7 +21263,7 @@
         <v>SLN1030</v>
       </c>
       <c r="C427" t="str">
-        <v>BB-X HYPER-REPEL α 漂浮 NL-I61Q</v>
+        <v>BB-X HYPER-REPEL α 漂浮 NL-I61Q | 5号</v>
       </c>
       <c r="D427" t="str">
         <v>白色</v>
@@ -21127,7 +21307,7 @@
         <v>SLN1030</v>
       </c>
       <c r="C428" t="str">
-        <v>BB-X HYPER-REPEL α 漂浮 NL-I61Q</v>
+        <v>BB-X HYPER-REPEL α 漂浮 NL-I61Q | 6号</v>
       </c>
       <c r="D428" t="str">
         <v>白色</v>
@@ -21171,7 +21351,7 @@
         <v>SLN1030</v>
       </c>
       <c r="C429" t="str">
-        <v>BB-X HYPER-REPEL α 漂浮 NL-I61Q</v>
+        <v>BB-X HYPER-REPEL α 漂浮 NL-I61Q | 8号</v>
       </c>
       <c r="D429" t="str">
         <v>白色</v>
@@ -21215,7 +21395,7 @@
         <v>SLN1030</v>
       </c>
       <c r="C430" t="str">
-        <v>BB-X HYPER-REPEL α 漂浮 NL-I61Q</v>
+        <v>BB-X HYPER-REPEL α 漂浮 NL-I61Q | 10号</v>
       </c>
       <c r="D430" t="str">
         <v>白色</v>
@@ -21303,7 +21483,7 @@
         <v>SLN1031</v>
       </c>
       <c r="C432" t="str">
-        <v>BB-X PLASMA WHITE FLOAT LA-C54Y</v>
+        <v>BB-X PLASMA WHITE FLOAT LA-C54Y | 2.0号</v>
       </c>
       <c r="D432" t="str">
         <v>白色</v>
@@ -21347,7 +21527,7 @@
         <v>SLN1031</v>
       </c>
       <c r="C433" t="str">
-        <v>BB-X PLASMA WHITE FLOAT LA-C54Y</v>
+        <v>BB-X PLASMA WHITE FLOAT LA-C54Y | 2.5号</v>
       </c>
       <c r="D433" t="str">
         <v>白色</v>
@@ -21391,7 +21571,7 @@
         <v>SLN1031</v>
       </c>
       <c r="C434" t="str">
-        <v>BB-X PLASMA WHITE FLOAT LA-C54Y</v>
+        <v>BB-X PLASMA WHITE FLOAT LA-C54Y | 3.0号</v>
       </c>
       <c r="D434" t="str">
         <v>白色</v>
@@ -21435,7 +21615,7 @@
         <v>SLN1031</v>
       </c>
       <c r="C435" t="str">
-        <v>BB-X PLASMA WHITE FLOAT LA-C54Y</v>
+        <v>BB-X PLASMA WHITE FLOAT LA-C54Y | 4.0号</v>
       </c>
       <c r="D435" t="str">
         <v>白色</v>
@@ -21479,7 +21659,7 @@
         <v>SLN1031</v>
       </c>
       <c r="C436" t="str">
-        <v>BB-X PLASMA WHITE FLOAT LA-C54Y</v>
+        <v>BB-X PLASMA WHITE FLOAT LA-C54Y | 5.0号</v>
       </c>
       <c r="D436" t="str">
         <v>白色</v>
@@ -21523,7 +21703,7 @@
         <v>SLN1031</v>
       </c>
       <c r="C437" t="str">
-        <v>BB-X PLASMA WHITE FLOAT LA-C54Y</v>
+        <v>BB-X PLASMA WHITE FLOAT LA-C54Y | 6.0号</v>
       </c>
       <c r="D437" t="str">
         <v>白色</v>
@@ -21567,7 +21747,7 @@
         <v>SLN1031</v>
       </c>
       <c r="C438" t="str">
-        <v>BB-X PLASMA WHITE FLOAT LA-C54Y</v>
+        <v>BB-X PLASMA WHITE FLOAT LA-C54Y | 8.0号</v>
       </c>
       <c r="D438" t="str">
         <v>白色</v>
@@ -21655,7 +21835,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C440" t="str">
-        <v>PITBULL 4 PL-M54R</v>
+        <v>PITBULL 4 PL-M54R | 0.5号</v>
       </c>
       <c r="D440" t="str">
         <v>绿色</v>
@@ -21699,7 +21879,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C441" t="str">
-        <v>PITBULL 4 PL-M54R</v>
+        <v>PITBULL 4 PL-M54R | 0.6号</v>
       </c>
       <c r="D441" t="str">
         <v>绿色</v>
@@ -21743,7 +21923,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C442" t="str">
-        <v>PITBULL 4 PL-M54R</v>
+        <v>PITBULL 4 PL-M54R | 0.8号</v>
       </c>
       <c r="D442" t="str">
         <v>绿色</v>
@@ -21787,7 +21967,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C443" t="str">
-        <v>PITBULL 4 PL-M54R</v>
+        <v>PITBULL 4 PL-M54R | 1号</v>
       </c>
       <c r="D443" t="str">
         <v>绿色</v>
@@ -21831,7 +22011,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C444" t="str">
-        <v>PITBULL 4 PL-M54R</v>
+        <v>PITBULL 4 PL-M54R | 1.2号</v>
       </c>
       <c r="D444" t="str">
         <v>绿色</v>
@@ -21875,7 +22055,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C445" t="str">
-        <v>PITBULL 4 PL-M54R</v>
+        <v>PITBULL 4 PL-M54R | 1.5号</v>
       </c>
       <c r="D445" t="str">
         <v>绿色</v>
@@ -21919,7 +22099,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C446" t="str">
-        <v>PITBULL 4 PL-M54R</v>
+        <v>PITBULL 4 PL-M54R | 2号</v>
       </c>
       <c r="D446" t="str">
         <v>绿色</v>
@@ -22007,7 +22187,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C448" t="str">
-        <v>PITBULL 4 PL-M64R</v>
+        <v>PITBULL 4 PL-M64R | 0.5号</v>
       </c>
       <c r="D448" t="str">
         <v>绿色</v>
@@ -22051,7 +22231,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C449" t="str">
-        <v>PITBULL 4 PL-M64R</v>
+        <v>PITBULL 4 PL-M64R | 0.6号</v>
       </c>
       <c r="D449" t="str">
         <v>绿色</v>
@@ -22095,7 +22275,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C450" t="str">
-        <v>PITBULL 4 PL-M64R</v>
+        <v>PITBULL 4 PL-M64R | 0.8号</v>
       </c>
       <c r="D450" t="str">
         <v>绿色</v>
@@ -22139,7 +22319,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C451" t="str">
-        <v>PITBULL 4 PL-M64R</v>
+        <v>PITBULL 4 PL-M64R | 1号</v>
       </c>
       <c r="D451" t="str">
         <v>绿色</v>
@@ -22183,7 +22363,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C452" t="str">
-        <v>PITBULL 4 PL-M64R</v>
+        <v>PITBULL 4 PL-M64R | 1.2号</v>
       </c>
       <c r="D452" t="str">
         <v>绿色</v>
@@ -22227,7 +22407,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C453" t="str">
-        <v>PITBULL 4 PL-M64R</v>
+        <v>PITBULL 4 PL-M64R | 1.5号</v>
       </c>
       <c r="D453" t="str">
         <v>绿色</v>
@@ -22271,7 +22451,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C454" t="str">
-        <v>PITBULL 4 PL-M64R</v>
+        <v>PITBULL 4 PL-M64R | 2号</v>
       </c>
       <c r="D454" t="str">
         <v>绿色</v>
@@ -22359,7 +22539,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C456" t="str">
-        <v>PITBULL 4 PL-M74S</v>
+        <v>PITBULL 4 PL-M74S | 1号</v>
       </c>
       <c r="D456" t="str">
         <v>绿色</v>
@@ -22403,7 +22583,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C457" t="str">
-        <v>PITBULL 4 PL-M74S</v>
+        <v>PITBULL 4 PL-M74S | 1.2号</v>
       </c>
       <c r="D457" t="str">
         <v>绿色</v>
@@ -22447,7 +22627,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C458" t="str">
-        <v>PITBULL 4 PL-M74S</v>
+        <v>PITBULL 4 PL-M74S | 1.5号</v>
       </c>
       <c r="D458" t="str">
         <v>绿色</v>
@@ -22491,7 +22671,7 @@
         <v>SLN1032</v>
       </c>
       <c r="C459" t="str">
-        <v>PITBULL 4 PL-M74S</v>
+        <v>PITBULL 4 PL-M74S | 2号</v>
       </c>
       <c r="D459" t="str">
         <v>绿色</v>
@@ -22579,7 +22759,7 @@
         <v>SLN1033</v>
       </c>
       <c r="C461" t="str">
-        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮 NL-I54Q</v>
+        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮 NL-I54Q | 1.7号</v>
       </c>
       <c r="D461" t="str">
         <v>金色</v>
@@ -22623,7 +22803,7 @@
         <v>SLN1033</v>
       </c>
       <c r="C462" t="str">
-        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮 NL-I54Q</v>
+        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮 NL-I54Q | 2号</v>
       </c>
       <c r="D462" t="str">
         <v>金色</v>
@@ -22667,7 +22847,7 @@
         <v>SLN1033</v>
       </c>
       <c r="C463" t="str">
-        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮 NL-I54Q</v>
+        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮 NL-I54Q | 2.5号</v>
       </c>
       <c r="D463" t="str">
         <v>金色</v>
@@ -22711,7 +22891,7 @@
         <v>SLN1033</v>
       </c>
       <c r="C464" t="str">
-        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮 NL-I54Q</v>
+        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮 NL-I54Q | 3号</v>
       </c>
       <c r="D464" t="str">
         <v>金色</v>
@@ -22755,7 +22935,7 @@
         <v>SLN1033</v>
       </c>
       <c r="C465" t="str">
-        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮 NL-I54Q</v>
+        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮 NL-I54Q | 4号</v>
       </c>
       <c r="D465" t="str">
         <v>金色</v>
@@ -22843,7 +23023,7 @@
         <v>SLN1034</v>
       </c>
       <c r="C467" t="str">
-        <v>LIMITED PRO 矶 ZERO 悬停 150m NL-I55R</v>
+        <v>LIMITED PRO 矶 ZERO 悬停 150m NL-I55R | 1.7号</v>
       </c>
       <c r="D467" t="str">
         <v>红色</v>
@@ -22887,7 +23067,7 @@
         <v>SLN1034</v>
       </c>
       <c r="C468" t="str">
-        <v>LIMITED PRO 矶 ZERO 悬停 150m NL-I55R</v>
+        <v>LIMITED PRO 矶 ZERO 悬停 150m NL-I55R | 2号</v>
       </c>
       <c r="D468" t="str">
         <v>红色</v>
@@ -22931,7 +23111,7 @@
         <v>SLN1034</v>
       </c>
       <c r="C469" t="str">
-        <v>LIMITED PRO 矶 ZERO 悬停 150m NL-I55R</v>
+        <v>LIMITED PRO 矶 ZERO 悬停 150m NL-I55R | 2.5号</v>
       </c>
       <c r="D469" t="str">
         <v>红色</v>
@@ -22975,7 +23155,7 @@
         <v>SLN1034</v>
       </c>
       <c r="C470" t="str">
-        <v>LIMITED PRO 矶 ZERO 悬停 150m NL-I55R</v>
+        <v>LIMITED PRO 矶 ZERO 悬停 150m NL-I55R | 3号</v>
       </c>
       <c r="D470" t="str">
         <v>红色</v>
@@ -23019,7 +23199,7 @@
         <v>SLN1034</v>
       </c>
       <c r="C471" t="str">
-        <v>LIMITED PRO 矶 ZERO 悬停 150m NL-I55R</v>
+        <v>LIMITED PRO 矶 ZERO 悬停 150m NL-I55R | 4号</v>
       </c>
       <c r="D471" t="str">
         <v>红色</v>
@@ -23107,7 +23287,7 @@
         <v>SLN1035</v>
       </c>
       <c r="C473" t="str">
-        <v>BB-X PLASMA WHITE ZERO SUSPEND LA-C55Y</v>
+        <v>BB-X PLASMA WHITE ZERO SUSPEND LA-C55Y | 1.75号</v>
       </c>
       <c r="D473" t="str">
         <v>白色</v>
@@ -23151,7 +23331,7 @@
         <v>SLN1035</v>
       </c>
       <c r="C474" t="str">
-        <v>BB-X PLASMA WHITE ZERO SUSPEND LA-C55Y</v>
+        <v>BB-X PLASMA WHITE ZERO SUSPEND LA-C55Y | 2.0号</v>
       </c>
       <c r="D474" t="str">
         <v>白色</v>
@@ -23195,7 +23375,7 @@
         <v>SLN1035</v>
       </c>
       <c r="C475" t="str">
-        <v>BB-X PLASMA WHITE ZERO SUSPEND LA-C55Y</v>
+        <v>BB-X PLASMA WHITE ZERO SUSPEND LA-C55Y | 2.5号</v>
       </c>
       <c r="D475" t="str">
         <v>白色</v>
@@ -23239,7 +23419,7 @@
         <v>SLN1035</v>
       </c>
       <c r="C476" t="str">
-        <v>BB-X PLASMA WHITE ZERO SUSPEND LA-C55Y</v>
+        <v>BB-X PLASMA WHITE ZERO SUSPEND LA-C55Y | 3.0号</v>
       </c>
       <c r="D476" t="str">
         <v>白色</v>
@@ -23283,7 +23463,7 @@
         <v>SLN1035</v>
       </c>
       <c r="C477" t="str">
-        <v>BB-X PLASMA WHITE ZERO SUSPEND LA-C55Y</v>
+        <v>BB-X PLASMA WHITE ZERO SUSPEND LA-C55Y | 4.0号</v>
       </c>
       <c r="D477" t="str">
         <v>白色</v>
@@ -23371,7 +23551,7 @@
         <v>SLN1036</v>
       </c>
       <c r="C479" t="str">
-        <v>MASTIFF FC 90m LB-B41V</v>
+        <v>MASTIFF FC 90m LB-B41V | 90m</v>
       </c>
       <c r="D479" t="str">
         <v>透明色</v>
@@ -23415,7 +23595,7 @@
         <v>SLN1036</v>
       </c>
       <c r="C480" t="str">
-        <v>MASTIFF FC 90m LB-B41V</v>
+        <v>MASTIFF FC 90m LB-B41V | 90m | 868565</v>
       </c>
       <c r="D480" t="str">
         <v>透明色</v>
@@ -23459,7 +23639,7 @@
         <v>SLN1036</v>
       </c>
       <c r="C481" t="str">
-        <v>MASTIFF FC 90m LB-B41V</v>
+        <v>MASTIFF FC 90m LB-B41V | 90m | 868572</v>
       </c>
       <c r="D481" t="str">
         <v>透明色</v>
@@ -23503,7 +23683,7 @@
         <v>SLN1036</v>
       </c>
       <c r="C482" t="str">
-        <v>MASTIFF FC 90m LB-B41V</v>
+        <v>MASTIFF FC 90m LB-B41V | 90m | 868619</v>
       </c>
       <c r="D482" t="str">
         <v>透明色</v>
@@ -23547,7 +23727,7 @@
         <v>SLN1036</v>
       </c>
       <c r="C483" t="str">
-        <v>MASTIFF FC 90m LB-B41V</v>
+        <v>MASTIFF FC 90m LB-B41V | 90m | 868626</v>
       </c>
       <c r="D483" t="str">
         <v>透明色</v>
@@ -23591,7 +23771,7 @@
         <v>SLN1036</v>
       </c>
       <c r="C484" t="str">
-        <v>MASTIFF FC 90m LB-B41V</v>
+        <v>MASTIFF FC 90m LB-B41V | 90m | 868633</v>
       </c>
       <c r="D484" t="str">
         <v>透明色</v>
@@ -23635,7 +23815,7 @@
         <v>SLN1036</v>
       </c>
       <c r="C485" t="str">
-        <v>MASTIFF FC 90m LB-B41V</v>
+        <v>MASTIFF FC 90m LB-B41V | 90m | 868640</v>
       </c>
       <c r="D485" t="str">
         <v>透明色</v>
@@ -23679,7 +23859,7 @@
         <v>SLN1036</v>
       </c>
       <c r="C486" t="str">
-        <v>MASTIFF FC 90m LB-B41V</v>
+        <v>MASTIFF FC 90m LB-B41V | 90m | 868657</v>
       </c>
       <c r="D486" t="str">
         <v>透明色</v>
@@ -23723,7 +23903,7 @@
         <v>SLN1036</v>
       </c>
       <c r="C487" t="str">
-        <v>MASTIFF FC 90m LB-B41V</v>
+        <v>MASTIFF FC 90m LB-B41V | 90m | 868664</v>
       </c>
       <c r="D487" t="str">
         <v>透明色</v>
@@ -23767,7 +23947,7 @@
         <v>SLN1036</v>
       </c>
       <c r="C488" t="str">
-        <v>MASTIFF FC 90m LB-B41V</v>
+        <v>MASTIFF FC 90m LB-B41V | 90m | 868671</v>
       </c>
       <c r="D488" t="str">
         <v>透明色</v>
@@ -23855,7 +24035,7 @@
         <v>SLN1037</v>
       </c>
       <c r="C490" t="str">
-        <v>OCEA 前导线 LA-A21U</v>
+        <v>OCEA 前导线 LA-A21U | 60号</v>
       </c>
       <c r="D490" t="str">
         <v>透明色</v>
@@ -23899,7 +24079,7 @@
         <v>SLN1037</v>
       </c>
       <c r="C491" t="str">
-        <v>OCEA 前导线 LA-A21U</v>
+        <v>OCEA 前导线 LA-A21U | 80号</v>
       </c>
       <c r="D491" t="str">
         <v>透明色</v>
@@ -23987,7 +24167,7 @@
         <v>SLN1037</v>
       </c>
       <c r="C493" t="str">
-        <v>OCEA 前导线 LA-A31U</v>
+        <v>OCEA 前导线 LA-A31U | 14号</v>
       </c>
       <c r="D493" t="str">
         <v>透明色</v>
@@ -24031,7 +24211,7 @@
         <v>SLN1037</v>
       </c>
       <c r="C494" t="str">
-        <v>OCEA 前导线 LA-A31U</v>
+        <v>OCEA 前导线 LA-A31U | 18号</v>
       </c>
       <c r="D494" t="str">
         <v>透明色</v>
@@ -24075,7 +24255,7 @@
         <v>SLN1037</v>
       </c>
       <c r="C495" t="str">
-        <v>OCEA 前导线 LA-A31U</v>
+        <v>OCEA 前导线 LA-A31U | 22号</v>
       </c>
       <c r="D495" t="str">
         <v>透明色</v>
@@ -24119,7 +24299,7 @@
         <v>SLN1037</v>
       </c>
       <c r="C496" t="str">
-        <v>OCEA 前导线 LA-A31U</v>
+        <v>OCEA 前导线 LA-A31U | 24号</v>
       </c>
       <c r="D496" t="str">
         <v>透明色</v>
@@ -24163,7 +24343,7 @@
         <v>SLN1037</v>
       </c>
       <c r="C497" t="str">
-        <v>OCEA 前导线 LA-A31U</v>
+        <v>OCEA 前导线 LA-A31U | 28号</v>
       </c>
       <c r="D497" t="str">
         <v>透明色</v>
@@ -24207,7 +24387,7 @@
         <v>SLN1037</v>
       </c>
       <c r="C498" t="str">
-        <v>OCEA 前导线 LA-A31U</v>
+        <v>OCEA 前导线 LA-A31U | 30号</v>
       </c>
       <c r="D498" t="str">
         <v>透明色</v>
@@ -24251,7 +24431,7 @@
         <v>SLN1037</v>
       </c>
       <c r="C499" t="str">
-        <v>OCEA 前导线 LA-A31U</v>
+        <v>OCEA 前导线 LA-A31U | 35号</v>
       </c>
       <c r="D499" t="str">
         <v>透明色</v>
@@ -24295,7 +24475,7 @@
         <v>SLN1037</v>
       </c>
       <c r="C500" t="str">
-        <v>OCEA 前导线 LA-A31U</v>
+        <v>OCEA 前导线 LA-A31U | 40号</v>
       </c>
       <c r="D500" t="str">
         <v>透明色</v>
@@ -24383,7 +24563,7 @@
         <v>SLN1038</v>
       </c>
       <c r="C502" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮 NL-I51P</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮 NL-I51P | 1.7号</v>
       </c>
       <c r="D502" t="str">
         <v>粉色</v>
@@ -24427,7 +24607,7 @@
         <v>SLN1038</v>
       </c>
       <c r="C503" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮 NL-I51P</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮 NL-I51P | 2号</v>
       </c>
       <c r="D503" t="str">
         <v>粉色</v>
@@ -24471,7 +24651,7 @@
         <v>SLN1038</v>
       </c>
       <c r="C504" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮 NL-I51P</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮 NL-I51P | 2.5号</v>
       </c>
       <c r="D504" t="str">
         <v>粉色</v>
@@ -24515,7 +24695,7 @@
         <v>SLN1038</v>
       </c>
       <c r="C505" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮 NL-I51P</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮 NL-I51P | 3号</v>
       </c>
       <c r="D505" t="str">
         <v>粉色</v>
@@ -24559,7 +24739,7 @@
         <v>SLN1038</v>
       </c>
       <c r="C506" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮 NL-I51P</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮 NL-I51P | 4号</v>
       </c>
       <c r="D506" t="str">
         <v>粉色</v>
@@ -24647,7 +24827,7 @@
         <v>SLN1039</v>
       </c>
       <c r="C508" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停 NL-I52P</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停 NL-I52P | 1.7号</v>
       </c>
       <c r="D508" t="str">
         <v>黄绿色</v>
@@ -24691,7 +24871,7 @@
         <v>SLN1039</v>
       </c>
       <c r="C509" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停 NL-I52P</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停 NL-I52P | 2号</v>
       </c>
       <c r="D509" t="str">
         <v>黄绿色</v>
@@ -24735,7 +24915,7 @@
         <v>SLN1039</v>
       </c>
       <c r="C510" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停 NL-I52P</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停 NL-I52P | 2.5号</v>
       </c>
       <c r="D510" t="str">
         <v>黄绿色</v>
@@ -24779,7 +24959,7 @@
         <v>SLN1039</v>
       </c>
       <c r="C511" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停 NL-I52P</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停 NL-I52P | 3号</v>
       </c>
       <c r="D511" t="str">
         <v>黄绿色</v>
@@ -24823,7 +25003,7 @@
         <v>SLN1039</v>
       </c>
       <c r="C512" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停 NL-I52P</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停 NL-I52P | 4号</v>
       </c>
       <c r="D512" t="str">
         <v>黄绿色</v>
@@ -24911,7 +25091,7 @@
         <v>SLN1040</v>
       </c>
       <c r="C514" t="str">
-        <v>BB-X HYPER-REPEL α 悬停 NL-I52Q</v>
+        <v>BB-X HYPER-REPEL α 悬停 NL-I52Q | 2号</v>
       </c>
       <c r="D514" t="str">
         <v>白色</v>
@@ -24955,7 +25135,7 @@
         <v>SLN1040</v>
       </c>
       <c r="C515" t="str">
-        <v>BB-X HYPER-REPEL α 悬停 NL-I52Q</v>
+        <v>BB-X HYPER-REPEL α 悬停 NL-I52Q | 2.5号</v>
       </c>
       <c r="D515" t="str">
         <v>白色</v>
@@ -24999,7 +25179,7 @@
         <v>SLN1040</v>
       </c>
       <c r="C516" t="str">
-        <v>BB-X HYPER-REPEL α 悬停 NL-I52Q</v>
+        <v>BB-X HYPER-REPEL α 悬停 NL-I52Q | 3号</v>
       </c>
       <c r="D516" t="str">
         <v>白色</v>
@@ -25043,7 +25223,7 @@
         <v>SLN1040</v>
       </c>
       <c r="C517" t="str">
-        <v>BB-X HYPER-REPEL α 悬停 NL-I52Q</v>
+        <v>BB-X HYPER-REPEL α 悬停 NL-I52Q | 4号</v>
       </c>
       <c r="D517" t="str">
         <v>白色</v>
@@ -25131,7 +25311,7 @@
         <v>SLN1041</v>
       </c>
       <c r="C519" t="str">
-        <v>OCEA 16 30m LD-A21Y</v>
+        <v>OCEA 16 30m LD-A21Y | 6号</v>
       </c>
       <c r="D519" t="str">
         <v>蓝色</v>
@@ -25175,7 +25355,7 @@
         <v>SLN1041</v>
       </c>
       <c r="C520" t="str">
-        <v>OCEA 16 30m LD-A21Y</v>
+        <v>OCEA 16 30m LD-A21Y | 8号</v>
       </c>
       <c r="D520" t="str">
         <v>蓝色</v>
@@ -25219,7 +25399,7 @@
         <v>SLN1041</v>
       </c>
       <c r="C521" t="str">
-        <v>OCEA 16 30m LD-A21Y</v>
+        <v>OCEA 16 30m LD-A21Y | 10号</v>
       </c>
       <c r="D521" t="str">
         <v>蓝色</v>
@@ -25307,7 +25487,7 @@
         <v>SLN1042</v>
       </c>
       <c r="C523" t="str">
-        <v>PITBULL 4+ LD-M44V</v>
+        <v>PITBULL 4+ LD-M44V | 100m</v>
       </c>
       <c r="D523" t="str">
         <v>粉色</v>
@@ -25351,7 +25531,7 @@
         <v>SLN1042</v>
       </c>
       <c r="C524" t="str">
-        <v>PITBULL 4+ LD-M44V</v>
+        <v>PITBULL 4+ LD-M44V | 100m | 7.1lb</v>
       </c>
       <c r="D524" t="str">
         <v>粉色</v>
@@ -25395,7 +25575,7 @@
         <v>SLN1042</v>
       </c>
       <c r="C525" t="str">
-        <v>PITBULL 4+ LD-M44V</v>
+        <v>PITBULL 4+ LD-M44V | 100m | 4.5lb</v>
       </c>
       <c r="D525" t="str">
         <v>灰色</v>
@@ -25439,7 +25619,7 @@
         <v>SLN1042</v>
       </c>
       <c r="C526" t="str">
-        <v>PITBULL 4+ LD-M44V</v>
+        <v>PITBULL 4+ LD-M44V | 100m | 5.6lb</v>
       </c>
       <c r="D526" t="str">
         <v>灰色</v>
@@ -25483,7 +25663,7 @@
         <v>SLN1042</v>
       </c>
       <c r="C527" t="str">
-        <v>PITBULL 4+ LD-M44V</v>
+        <v>PITBULL 4+ LD-M44V | 100m | 7.1lb | 818157</v>
       </c>
       <c r="D527" t="str">
         <v>灰色</v>
@@ -25571,7 +25751,7 @@
         <v>SLN1043</v>
       </c>
       <c r="C529" t="str">
-        <v>BASIS G5 PE SUSPEND LD-C59Y</v>
+        <v>BASIS G5 PE SUSPEND LD-C59Y | 0.8号</v>
       </c>
       <c r="D529" t="str">
         <v>黄色</v>
@@ -25615,7 +25795,7 @@
         <v>SLN1043</v>
       </c>
       <c r="C530" t="str">
-        <v>BASIS G5 PE SUSPEND LD-C59Y</v>
+        <v>BASIS G5 PE SUSPEND LD-C59Y | 1号</v>
       </c>
       <c r="D530" t="str">
         <v>黄色</v>
@@ -25703,7 +25883,7 @@
         <v>SLN1044</v>
       </c>
       <c r="C532" t="str">
-        <v>FIREBLOOD STRETCH 悬停 LA-C51T</v>
+        <v>FIREBLOOD STRETCH 悬停 LA-C51T | 1.75号</v>
       </c>
       <c r="D532" t="str">
         <v>荧光绿</v>
@@ -25747,7 +25927,7 @@
         <v>SLN1044</v>
       </c>
       <c r="C533" t="str">
-        <v>FIREBLOOD STRETCH 悬停 LA-C51T</v>
+        <v>FIREBLOOD STRETCH 悬停 LA-C51T | 2号</v>
       </c>
       <c r="D533" t="str">
         <v>荧光绿</v>
@@ -25791,7 +25971,7 @@
         <v>SLN1044</v>
       </c>
       <c r="C534" t="str">
-        <v>FIREBLOOD STRETCH 悬停 LA-C51T</v>
+        <v>FIREBLOOD STRETCH 悬停 LA-C51T | 2.5号</v>
       </c>
       <c r="D534" t="str">
         <v>荧光绿</v>
@@ -25835,7 +26015,7 @@
         <v>SLN1044</v>
       </c>
       <c r="C535" t="str">
-        <v>FIREBLOOD STRETCH 悬停 LA-C51T</v>
+        <v>FIREBLOOD STRETCH 悬停 LA-C51T | 3号</v>
       </c>
       <c r="D535" t="str">
         <v>荧光绿</v>
@@ -25879,7 +26059,7 @@
         <v>SLN1044</v>
       </c>
       <c r="C536" t="str">
-        <v>FIREBLOOD STRETCH 悬停 LA-C51T</v>
+        <v>FIREBLOOD STRETCH 悬停 LA-C51T | 4号</v>
       </c>
       <c r="D536" t="str">
         <v>荧光绿</v>
@@ -25923,7 +26103,7 @@
         <v>SLN1044</v>
       </c>
       <c r="C537" t="str">
-        <v>FIREBLOOD STRETCH 悬停 LA-C51T</v>
+        <v>FIREBLOOD STRETCH 悬停 LA-C51T | 5号</v>
       </c>
       <c r="D537" t="str">
         <v>荧光绿</v>
@@ -25967,7 +26147,7 @@
         <v>SLN1044</v>
       </c>
       <c r="C538" t="str">
-        <v>FIREBLOOD STRETCH 悬停 LA-C51T</v>
+        <v>FIREBLOOD STRETCH 悬停 LA-C51T | 6号</v>
       </c>
       <c r="D538" t="str">
         <v>荧光绿</v>
@@ -26055,7 +26235,7 @@
         <v>SLN1045</v>
       </c>
       <c r="C540" t="str">
-        <v>SIGHT LASER EX 240m CL-L75Q</v>
+        <v>SIGHT LASER EX 240m CL-L75Q | 0.25号</v>
       </c>
       <c r="D540" t="str">
         <v>橙色</v>
@@ -26099,7 +26279,7 @@
         <v>SLN1045</v>
       </c>
       <c r="C541" t="str">
-        <v>SIGHT LASER EX 240m CL-L75Q</v>
+        <v>SIGHT LASER EX 240m CL-L75Q | 0.3号</v>
       </c>
       <c r="D541" t="str">
         <v>橙色</v>
@@ -26143,7 +26323,7 @@
         <v>SLN1045</v>
       </c>
       <c r="C542" t="str">
-        <v>SIGHT LASER EX 240m CL-L75Q</v>
+        <v>SIGHT LASER EX 240m CL-L75Q | 0.4号</v>
       </c>
       <c r="D542" t="str">
         <v>橙色</v>
@@ -26187,7 +26367,7 @@
         <v>SLN1045</v>
       </c>
       <c r="C543" t="str">
-        <v>SIGHT LASER EX 240m CL-L75Q</v>
+        <v>SIGHT LASER EX 240m CL-L75Q | 0.5号</v>
       </c>
       <c r="D543" t="str">
         <v>橙色</v>
@@ -26231,7 +26411,7 @@
         <v>SLN1045</v>
       </c>
       <c r="C544" t="str">
-        <v>SIGHT LASER EX 240m CL-L75Q</v>
+        <v>SIGHT LASER EX 240m CL-L75Q | 0.2号</v>
       </c>
       <c r="D544" t="str">
         <v>荧光绿</v>
@@ -26275,7 +26455,7 @@
         <v>SLN1045</v>
       </c>
       <c r="C545" t="str">
-        <v>SIGHT LASER EX 240m CL-L75Q</v>
+        <v>SIGHT LASER EX 240m CL-L75Q | 0.25号 | 240m</v>
       </c>
       <c r="D545" t="str">
         <v>荧光绿</v>
@@ -26319,7 +26499,7 @@
         <v>SLN1045</v>
       </c>
       <c r="C546" t="str">
-        <v>SIGHT LASER EX 240m CL-L75Q</v>
+        <v>SIGHT LASER EX 240m CL-L75Q | 0.3号 | 240m</v>
       </c>
       <c r="D546" t="str">
         <v>荧光绿</v>
@@ -26363,7 +26543,7 @@
         <v>SLN1045</v>
       </c>
       <c r="C547" t="str">
-        <v>SIGHT LASER EX 240m CL-L75Q</v>
+        <v>SIGHT LASER EX 240m CL-L75Q | 0.4号 | 240m</v>
       </c>
       <c r="D547" t="str">
         <v>荧光绿</v>
@@ -26407,7 +26587,7 @@
         <v>SLN1045</v>
       </c>
       <c r="C548" t="str">
-        <v>SIGHT LASER EX 240m CL-L75Q</v>
+        <v>SIGHT LASER EX 240m CL-L75Q | 0.5号 | 240m</v>
       </c>
       <c r="D548" t="str">
         <v>荧光绿</v>
@@ -26495,7 +26675,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C550" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m</v>
       </c>
       <c r="D550" t="str">
         <v>灰色</v>
@@ -26539,7 +26719,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C551" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m | 16.7lb</v>
       </c>
       <c r="D551" t="str">
         <v>灰色</v>
@@ -26583,7 +26763,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C552" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m | 22.8lb</v>
       </c>
       <c r="D552" t="str">
         <v>灰色</v>
@@ -26627,7 +26807,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C553" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m | 25.8lb</v>
       </c>
       <c r="D553" t="str">
         <v>灰色</v>
@@ -26671,7 +26851,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C554" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m | 30.6lb</v>
       </c>
       <c r="D554" t="str">
         <v>灰色</v>
@@ -26715,7 +26895,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C555" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m | 10.6lb</v>
       </c>
       <c r="D555" t="str">
         <v>橙色</v>
@@ -26759,7 +26939,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C556" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m | 13.7lb</v>
       </c>
       <c r="D556" t="str">
         <v>橙色</v>
@@ -26803,7 +26983,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C557" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m | 16.7lb | 516022</v>
       </c>
       <c r="D557" t="str">
         <v>橙色</v>
@@ -26847,7 +27027,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C558" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m | 22.8lb | 516039</v>
       </c>
       <c r="D558" t="str">
         <v>橙色</v>
@@ -26891,7 +27071,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C559" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m | 25.8lb | 516046</v>
       </c>
       <c r="D559" t="str">
         <v>橙色</v>
@@ -26935,7 +27115,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C560" t="str">
-        <v>PITBULL G5 LD-M41U</v>
+        <v>PITBULL G5 LD-M41U | 100m | 30.6lb | 516053</v>
       </c>
       <c r="D560" t="str">
         <v>橙色</v>
@@ -27023,7 +27203,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C562" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m</v>
       </c>
       <c r="D562" t="str">
         <v>灰色</v>
@@ -27067,7 +27247,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C563" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m | 16.7lb</v>
       </c>
       <c r="D563" t="str">
         <v>灰色</v>
@@ -27111,7 +27291,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C564" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m | 22.8lb</v>
       </c>
       <c r="D564" t="str">
         <v>灰色</v>
@@ -27155,7 +27335,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C565" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m | 25.8lb</v>
       </c>
       <c r="D565" t="str">
         <v>灰色</v>
@@ -27199,7 +27379,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C566" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m | 30.6lb</v>
       </c>
       <c r="D566" t="str">
         <v>灰色</v>
@@ -27243,7 +27423,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C567" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m | 10.6lb</v>
       </c>
       <c r="D567" t="str">
         <v>橙色</v>
@@ -27287,7 +27467,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C568" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m | 13.7lb</v>
       </c>
       <c r="D568" t="str">
         <v>橙色</v>
@@ -27331,7 +27511,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C569" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m | 16.7lb | 516145</v>
       </c>
       <c r="D569" t="str">
         <v>橙色</v>
@@ -27375,7 +27555,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C570" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m | 22.8lb | 516152</v>
       </c>
       <c r="D570" t="str">
         <v>橙色</v>
@@ -27419,7 +27599,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C571" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m | 25.8lb | 516169</v>
       </c>
       <c r="D571" t="str">
         <v>橙色</v>
@@ -27463,7 +27643,7 @@
         <v>SLN1046</v>
       </c>
       <c r="C572" t="str">
-        <v>PITBULL G5 LD-M51U</v>
+        <v>PITBULL G5 LD-M51U | 150m | 30.6lb | 516176</v>
       </c>
       <c r="D572" t="str">
         <v>橙色</v>
@@ -27551,7 +27731,7 @@
         <v>SLN1047</v>
       </c>
       <c r="C574" t="str">
-        <v>Soare AJING 150m CL-L52N</v>
+        <v>Soare AJING 150m CL-L52N | 150m</v>
       </c>
       <c r="D574" t="str">
         <v>透明色</v>
@@ -27595,7 +27775,7 @@
         <v>SLN1047</v>
       </c>
       <c r="C575" t="str">
-        <v>Soare AJING 150m CL-L52N</v>
+        <v>Soare AJING 150m CL-L52N | 150m | 442628</v>
       </c>
       <c r="D575" t="str">
         <v>透明色</v>
@@ -27639,7 +27819,7 @@
         <v>SLN1047</v>
       </c>
       <c r="C576" t="str">
-        <v>Soare AJING 150m CL-L52N</v>
+        <v>Soare AJING 150m CL-L52N | 150m | 442635</v>
       </c>
       <c r="D576" t="str">
         <v>透明色</v>
@@ -27683,7 +27863,7 @@
         <v>SLN1047</v>
       </c>
       <c r="C577" t="str">
-        <v>Soare AJING 150m CL-L52N</v>
+        <v>Soare AJING 150m CL-L52N | 150m | 442642</v>
       </c>
       <c r="D577" t="str">
         <v>透明色</v>
@@ -27727,7 +27907,7 @@
         <v>SLN1047</v>
       </c>
       <c r="C578" t="str">
-        <v>Soare AJING 150m CL-L52N</v>
+        <v>Soare AJING 150m CL-L52N | 150m | 442659</v>
       </c>
       <c r="D578" t="str">
         <v>透明色</v>
@@ -27815,7 +27995,7 @@
         <v>SLN1048</v>
       </c>
       <c r="C580" t="str">
-        <v>Sephia MASTER 前导线 30m LB-E31T</v>
+        <v>Sephia MASTER 前导线 30m LB-E31T | 1.75号</v>
       </c>
       <c r="D580" t="str">
         <v>透明色</v>
@@ -27859,7 +28039,7 @@
         <v>SLN1048</v>
       </c>
       <c r="C581" t="str">
-        <v>Sephia MASTER 前导线 30m LB-E31T</v>
+        <v>Sephia MASTER 前导线 30m LB-E31T | 2号</v>
       </c>
       <c r="D581" t="str">
         <v>透明色</v>
@@ -27903,7 +28083,7 @@
         <v>SLN1048</v>
       </c>
       <c r="C582" t="str">
-        <v>Sephia MASTER 前导线 30m LB-E31T</v>
+        <v>Sephia MASTER 前导线 30m LB-E31T | 2.5号</v>
       </c>
       <c r="D582" t="str">
         <v>透明色</v>
@@ -27947,7 +28127,7 @@
         <v>SLN1048</v>
       </c>
       <c r="C583" t="str">
-        <v>Sephia MASTER 前导线 30m LB-E31T</v>
+        <v>Sephia MASTER 前导线 30m LB-E31T | 3号</v>
       </c>
       <c r="D583" t="str">
         <v>透明色</v>
@@ -28035,7 +28215,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C585" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 0.8号</v>
       </c>
       <c r="D585" t="str">
         <v>黄绿色</v>
@@ -28079,7 +28259,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C586" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 1.0号</v>
       </c>
       <c r="D586" t="str">
         <v>黄绿色</v>
@@ -28123,7 +28303,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C587" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 1.2号</v>
       </c>
       <c r="D587" t="str">
         <v>黄绿色</v>
@@ -28167,7 +28347,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C588" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 1.5号</v>
       </c>
       <c r="D588" t="str">
         <v>黄绿色</v>
@@ -28211,7 +28391,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C589" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 2.0号</v>
       </c>
       <c r="D589" t="str">
         <v>黄绿色</v>
@@ -28255,7 +28435,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C590" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 0.6号</v>
       </c>
       <c r="D590" t="str">
         <v>5色</v>
@@ -28299,7 +28479,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C591" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 0.8号 | 150m</v>
       </c>
       <c r="D591" t="str">
         <v>5色</v>
@@ -28343,7 +28523,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C592" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 1.0号 | 150m</v>
       </c>
       <c r="D592" t="str">
         <v>5色</v>
@@ -28387,7 +28567,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C593" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 1.2号 | 150m</v>
       </c>
       <c r="D593" t="str">
         <v>5色</v>
@@ -28431,7 +28611,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C594" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 1.5号 | 150m</v>
       </c>
       <c r="D594" t="str">
         <v>5色</v>
@@ -28475,7 +28655,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C595" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 2.0号 | 150m</v>
       </c>
       <c r="D595" t="str">
         <v>5色</v>
@@ -28519,7 +28699,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C596" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 0.6号 | 150m</v>
       </c>
       <c r="D596" t="str">
         <v>灰色</v>
@@ -28563,7 +28743,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C597" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 0.8号 | 150m | 151711</v>
       </c>
       <c r="D597" t="str">
         <v>灰色</v>
@@ -28607,7 +28787,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C598" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 1.0号 | 150m | 151728</v>
       </c>
       <c r="D598" t="str">
         <v>灰色</v>
@@ -28651,7 +28831,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C599" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 1.2号 | 150m | 151735</v>
       </c>
       <c r="D599" t="str">
         <v>灰色</v>
@@ -28695,7 +28875,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C600" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 1.5号 | 150m | 151742</v>
       </c>
       <c r="D600" t="str">
         <v>灰色</v>
@@ -28739,7 +28919,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C601" t="str">
-        <v>BB BRAID LD-M54Y</v>
+        <v>BB BRAID LD-M54Y | 2.0号 | 150m | 151414</v>
       </c>
       <c r="D601" t="str">
         <v>灰色</v>
@@ -28827,7 +29007,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C603" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 0.8号</v>
       </c>
       <c r="D603" t="str">
         <v>黄绿色</v>
@@ -28871,7 +29051,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C604" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 1.0号</v>
       </c>
       <c r="D604" t="str">
         <v>黄绿色</v>
@@ -28915,7 +29095,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C605" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 1.2号</v>
       </c>
       <c r="D605" t="str">
         <v>黄绿色</v>
@@ -28959,7 +29139,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C606" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 1.5号</v>
       </c>
       <c r="D606" t="str">
         <v>黄绿色</v>
@@ -29003,7 +29183,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C607" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 2.0号</v>
       </c>
       <c r="D607" t="str">
         <v>黄绿色</v>
@@ -29047,7 +29227,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C608" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 3.0号</v>
       </c>
       <c r="D608" t="str">
         <v>黄绿色</v>
@@ -29091,7 +29271,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C609" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 0.6号</v>
       </c>
       <c r="D609" t="str">
         <v>5色</v>
@@ -29135,7 +29315,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C610" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 0.8号 | 200m</v>
       </c>
       <c r="D610" t="str">
         <v>5色</v>
@@ -29179,7 +29359,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C611" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 1.0号 | 200m</v>
       </c>
       <c r="D611" t="str">
         <v>5色</v>
@@ -29223,7 +29403,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C612" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 1.2号 | 200m</v>
       </c>
       <c r="D612" t="str">
         <v>5色</v>
@@ -29267,7 +29447,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C613" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 1.5号 | 200m</v>
       </c>
       <c r="D613" t="str">
         <v>5色</v>
@@ -29311,7 +29491,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C614" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 2.0号 | 200m</v>
       </c>
       <c r="D614" t="str">
         <v>5色</v>
@@ -29355,7 +29535,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C615" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 3.0号 | 200m</v>
       </c>
       <c r="D615" t="str">
         <v>5色</v>
@@ -29399,7 +29579,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C616" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 0.6号 | 200m</v>
       </c>
       <c r="D616" t="str">
         <v>灰色</v>
@@ -29443,7 +29623,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C617" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 0.8号 | 200m | 151292</v>
       </c>
       <c r="D617" t="str">
         <v>灰色</v>
@@ -29487,7 +29667,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C618" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 1.0号 | 200m | 151308</v>
       </c>
       <c r="D618" t="str">
         <v>灰色</v>
@@ -29531,7 +29711,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C619" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 1.2号 | 200m | 151315</v>
       </c>
       <c r="D619" t="str">
         <v>灰色</v>
@@ -29575,7 +29755,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C620" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 1.5号 | 200m | 151322</v>
       </c>
       <c r="D620" t="str">
         <v>灰色</v>
@@ -29619,7 +29799,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C621" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 2.0号 | 200m | 151339</v>
       </c>
       <c r="D621" t="str">
         <v>灰色</v>
@@ -29663,7 +29843,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C622" t="str">
-        <v>BB BRAID LD-M64Y</v>
+        <v>BB BRAID LD-M64Y | 3.0号 | 200m | 151629</v>
       </c>
       <c r="D622" t="str">
         <v>灰色</v>
@@ -29751,7 +29931,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C624" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 0.8号</v>
       </c>
       <c r="D624" t="str">
         <v>黄绿色</v>
@@ -29795,7 +29975,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C625" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 1.0号</v>
       </c>
       <c r="D625" t="str">
         <v>黄绿色</v>
@@ -29839,7 +30019,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C626" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 1.2号</v>
       </c>
       <c r="D626" t="str">
         <v>黄绿色</v>
@@ -29883,7 +30063,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C627" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 1.5号</v>
       </c>
       <c r="D627" t="str">
         <v>黄绿色</v>
@@ -29927,7 +30107,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C628" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 2.0号</v>
       </c>
       <c r="D628" t="str">
         <v>黄绿色</v>
@@ -29971,7 +30151,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C629" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 3.0号</v>
       </c>
       <c r="D629" t="str">
         <v>黄绿色</v>
@@ -30015,7 +30195,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C630" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 0.6号</v>
       </c>
       <c r="D630" t="str">
         <v>5色</v>
@@ -30059,7 +30239,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C631" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 0.8号 | 300m</v>
       </c>
       <c r="D631" t="str">
         <v>5色</v>
@@ -30103,7 +30283,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C632" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 1.0号 | 300m</v>
       </c>
       <c r="D632" t="str">
         <v>5色</v>
@@ -30147,7 +30327,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C633" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 1.2号 | 300m</v>
       </c>
       <c r="D633" t="str">
         <v>5色</v>
@@ -30191,7 +30371,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C634" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 1.5号 | 300m</v>
       </c>
       <c r="D634" t="str">
         <v>5色</v>
@@ -30235,7 +30415,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C635" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 2.0号 | 300m</v>
       </c>
       <c r="D635" t="str">
         <v>5色</v>
@@ -30279,7 +30459,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C636" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 3.0号 | 300m</v>
       </c>
       <c r="D636" t="str">
         <v>5色</v>
@@ -30323,7 +30503,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C637" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 0.6号 | 300m</v>
       </c>
       <c r="D637" t="str">
         <v>灰色</v>
@@ -30367,7 +30547,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C638" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 0.8号 | 300m | 151360</v>
       </c>
       <c r="D638" t="str">
         <v>灰色</v>
@@ -30411,7 +30591,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C639" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 1.0号 | 300m | 151377</v>
       </c>
       <c r="D639" t="str">
         <v>灰色</v>
@@ -30455,7 +30635,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C640" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 1.2号 | 300m | 151384</v>
       </c>
       <c r="D640" t="str">
         <v>灰色</v>
@@ -30499,7 +30679,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C641" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 1.5号 | 300m | 151544</v>
       </c>
       <c r="D641" t="str">
         <v>灰色</v>
@@ -30543,7 +30723,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C642" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 2.0号 | 300m | 151551</v>
       </c>
       <c r="D642" t="str">
         <v>灰色</v>
@@ -30587,7 +30767,7 @@
         <v>SLN1049</v>
       </c>
       <c r="C643" t="str">
-        <v>BB BRAID LD-M74Y</v>
+        <v>BB BRAID LD-M74Y | 3.0号 | 300m | 150486</v>
       </c>
       <c r="D643" t="str">
         <v>灰色</v>
@@ -30675,7 +30855,7 @@
         <v>SLN1050</v>
       </c>
       <c r="C645" t="str">
-        <v>BAISIS 矶 NL-I57M</v>
+        <v>BAISIS 矶 NL-I57M | 1.7号</v>
       </c>
       <c r="D645" t="str">
         <v>黄色</v>
@@ -30719,7 +30899,7 @@
         <v>SLN1050</v>
       </c>
       <c r="C646" t="str">
-        <v>BAISIS 矶 NL-I57M</v>
+        <v>BAISIS 矶 NL-I57M | 2号</v>
       </c>
       <c r="D646" t="str">
         <v>黄色</v>
@@ -30763,7 +30943,7 @@
         <v>SLN1050</v>
       </c>
       <c r="C647" t="str">
-        <v>BAISIS 矶 NL-I57M</v>
+        <v>BAISIS 矶 NL-I57M | 2.5号</v>
       </c>
       <c r="D647" t="str">
         <v>黄色</v>
@@ -30807,7 +30987,7 @@
         <v>SLN1050</v>
       </c>
       <c r="C648" t="str">
-        <v>BAISIS 矶 NL-I57M</v>
+        <v>BAISIS 矶 NL-I57M | 3号</v>
       </c>
       <c r="D648" t="str">
         <v>黄色</v>
@@ -30851,7 +31031,7 @@
         <v>SLN1050</v>
       </c>
       <c r="C649" t="str">
-        <v>BAISIS 矶 NL-I57M</v>
+        <v>BAISIS 矶 NL-I57M | 4号</v>
       </c>
       <c r="D649" t="str">
         <v>黄色</v>
@@ -30895,7 +31075,7 @@
         <v>SLN1050</v>
       </c>
       <c r="C650" t="str">
-        <v>BAISIS 矶 NL-I57M</v>
+        <v>BAISIS 矶 NL-I57M | 5号</v>
       </c>
       <c r="D650" t="str">
         <v>黄色</v>
@@ -30939,7 +31119,7 @@
         <v>SLN1050</v>
       </c>
       <c r="C651" t="str">
-        <v>BAISIS 矶 NL-I57M</v>
+        <v>BAISIS 矶 NL-I57M | 6号</v>
       </c>
       <c r="D651" t="str">
         <v>黄色</v>
@@ -31027,7 +31207,7 @@
         <v>SLN1051</v>
       </c>
       <c r="C653" t="str">
-        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y</v>
+        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y | 1.75号</v>
       </c>
       <c r="D653" t="str">
         <v>橙色</v>
@@ -31071,7 +31251,7 @@
         <v>SLN1051</v>
       </c>
       <c r="C654" t="str">
-        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y</v>
+        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y | 2.0号</v>
       </c>
       <c r="D654" t="str">
         <v>橙色</v>
@@ -31115,7 +31295,7 @@
         <v>SLN1051</v>
       </c>
       <c r="C655" t="str">
-        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y</v>
+        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y | 2.5号</v>
       </c>
       <c r="D655" t="str">
         <v>橙色</v>
@@ -31159,7 +31339,7 @@
         <v>SLN1051</v>
       </c>
       <c r="C656" t="str">
-        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y</v>
+        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y | 3.0号</v>
       </c>
       <c r="D656" t="str">
         <v>橙色</v>
@@ -31203,7 +31383,7 @@
         <v>SLN1051</v>
       </c>
       <c r="C657" t="str">
-        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y</v>
+        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y | 4.0号</v>
       </c>
       <c r="D657" t="str">
         <v>橙色</v>
@@ -31247,7 +31427,7 @@
         <v>SLN1051</v>
       </c>
       <c r="C658" t="str">
-        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y</v>
+        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y | 5.0号</v>
       </c>
       <c r="D658" t="str">
         <v>橙色</v>
@@ -31291,7 +31471,7 @@
         <v>SLN1051</v>
       </c>
       <c r="C659" t="str">
-        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y</v>
+        <v>BASIS ORANGE ZERO SUSPEND LA-C53Y | 6.0号</v>
       </c>
       <c r="D659" t="str">
         <v>橙色</v>
@@ -31379,7 +31559,7 @@
         <v>SLN1052</v>
       </c>
       <c r="C661" t="str">
-        <v>BAISIS EX CL-I37M</v>
+        <v>BAISIS EX CL-I37M | 1.5号</v>
       </c>
       <c r="D661" t="str">
         <v>透明色</v>
@@ -31423,7 +31603,7 @@
         <v>SLN1052</v>
       </c>
       <c r="C662" t="str">
-        <v>BAISIS EX CL-I37M</v>
+        <v>BAISIS EX CL-I37M | 1.7号</v>
       </c>
       <c r="D662" t="str">
         <v>透明色</v>
@@ -31467,7 +31647,7 @@
         <v>SLN1052</v>
       </c>
       <c r="C663" t="str">
-        <v>BAISIS EX CL-I37M</v>
+        <v>BAISIS EX CL-I37M | 2号</v>
       </c>
       <c r="D663" t="str">
         <v>透明色</v>
@@ -31511,7 +31691,7 @@
         <v>SLN1052</v>
       </c>
       <c r="C664" t="str">
-        <v>BAISIS EX CL-I37M</v>
+        <v>BAISIS EX CL-I37M | 2.5号</v>
       </c>
       <c r="D664" t="str">
         <v>透明色</v>
@@ -31555,7 +31735,7 @@
         <v>SLN1052</v>
       </c>
       <c r="C665" t="str">
-        <v>BAISIS EX CL-I37M</v>
+        <v>BAISIS EX CL-I37M | 3号</v>
       </c>
       <c r="D665" t="str">
         <v>透明色</v>
@@ -31599,7 +31779,7 @@
         <v>SLN1052</v>
       </c>
       <c r="C666" t="str">
-        <v>BAISIS EX CL-I37M</v>
+        <v>BAISIS EX CL-I37M | 4号</v>
       </c>
       <c r="D666" t="str">
         <v>透明色</v>
@@ -31643,7 +31823,7 @@
         <v>SLN1052</v>
       </c>
       <c r="C667" t="str">
-        <v>BAISIS EX CL-I37M</v>
+        <v>BAISIS EX CL-I37M | 5号</v>
       </c>
       <c r="D667" t="str">
         <v>透明色</v>
@@ -31687,7 +31867,7 @@
         <v>SLN1052</v>
       </c>
       <c r="C668" t="str">
-        <v>BAISIS EX CL-I37M</v>
+        <v>BAISIS EX CL-I37M | 6号</v>
       </c>
       <c r="D668" t="str">
         <v>透明色</v>
@@ -31775,7 +31955,7 @@
         <v>SLN1053</v>
       </c>
       <c r="C670" t="str">
-        <v>EXSENCE 前导线 EX 30m CL-S23L</v>
+        <v>EXSENCE 前导线 EX 30m CL-S23L | 4号</v>
       </c>
       <c r="D670" t="str">
         <v>透明色</v>
@@ -31819,7 +31999,7 @@
         <v>SLN1053</v>
       </c>
       <c r="C671" t="str">
-        <v>EXSENCE 前导线 EX 30m CL-S23L</v>
+        <v>EXSENCE 前导线 EX 30m CL-S23L | 5号</v>
       </c>
       <c r="D671" t="str">
         <v>透明色</v>
@@ -31863,7 +32043,7 @@
         <v>SLN1053</v>
       </c>
       <c r="C672" t="str">
-        <v>EXSENCE 前导线 EX 30m CL-S23L</v>
+        <v>EXSENCE 前导线 EX 30m CL-S23L | 6号</v>
       </c>
       <c r="D672" t="str">
         <v>透明色</v>
@@ -31907,7 +32087,7 @@
         <v>SLN1053</v>
       </c>
       <c r="C673" t="str">
-        <v>EXSENCE 前导线 EX 30m CL-S23L</v>
+        <v>EXSENCE 前导线 EX 30m CL-S23L | 8号</v>
       </c>
       <c r="D673" t="str">
         <v>透明色</v>
@@ -31995,7 +32175,7 @@
         <v>SLN1054</v>
       </c>
       <c r="C675" t="str">
-        <v>炎月 EX 前导线 30m CL-G26P</v>
+        <v>炎月 EX 前导线 30m CL-G26P | 3号</v>
       </c>
       <c r="D675" t="str">
         <v>透明色</v>
@@ -32039,7 +32219,7 @@
         <v>SLN1054</v>
       </c>
       <c r="C676" t="str">
-        <v>炎月 EX 前导线 30m CL-G26P</v>
+        <v>炎月 EX 前导线 30m CL-G26P | 4号</v>
       </c>
       <c r="D676" t="str">
         <v>透明色</v>
@@ -32083,7 +32263,7 @@
         <v>SLN1054</v>
       </c>
       <c r="C677" t="str">
-        <v>炎月 EX 前导线 30m CL-G26P</v>
+        <v>炎月 EX 前导线 30m CL-G26P | 5号</v>
       </c>
       <c r="D677" t="str">
         <v>透明色</v>
@@ -32127,7 +32307,7 @@
         <v>SLN1054</v>
       </c>
       <c r="C678" t="str">
-        <v>炎月 EX 前导线 30m CL-G26P</v>
+        <v>炎月 EX 前导线 30m CL-G26P | 6号</v>
       </c>
       <c r="D678" t="str">
         <v>透明色</v>
@@ -32215,7 +32395,7 @@
         <v>SLN1055</v>
       </c>
       <c r="C680" t="str">
-        <v>Soare 前导线 EX 30m CL-L23K</v>
+        <v>Soare 前导线 EX 30m CL-L23K | 30m</v>
       </c>
       <c r="D680" t="str">
         <v>透明色</v>
@@ -32259,7 +32439,7 @@
         <v>SLN1055</v>
       </c>
       <c r="C681" t="str">
-        <v>Soare 前导线 EX 30m CL-L23K</v>
+        <v>Soare 前导线 EX 30m CL-L23K | 30m | 764393</v>
       </c>
       <c r="D681" t="str">
         <v>透明色</v>
@@ -32303,7 +32483,7 @@
         <v>SLN1055</v>
       </c>
       <c r="C682" t="str">
-        <v>Soare 前导线 EX 30m CL-L23K</v>
+        <v>Soare 前导线 EX 30m CL-L23K | 30m | 764409</v>
       </c>
       <c r="D682" t="str">
         <v>透明色</v>
@@ -32347,7 +32527,7 @@
         <v>SLN1055</v>
       </c>
       <c r="C683" t="str">
-        <v>Soare 前导线 EX 30m CL-L23K</v>
+        <v>Soare 前导线 EX 30m CL-L23K | 30m | 764416</v>
       </c>
       <c r="D683" t="str">
         <v>透明色</v>
@@ -32435,7 +32615,7 @@
         <v>SLN1056</v>
       </c>
       <c r="C685" t="str">
-        <v>Sephia 前导线 30m LB-E21S</v>
+        <v>Sephia 前导线 30m LB-E21S | 1.75号</v>
       </c>
       <c r="D685" t="str">
         <v>透明色</v>
@@ -32479,7 +32659,7 @@
         <v>SLN1056</v>
       </c>
       <c r="C686" t="str">
-        <v>Sephia 前导线 30m LB-E21S</v>
+        <v>Sephia 前导线 30m LB-E21S | 2号</v>
       </c>
       <c r="D686" t="str">
         <v>透明色</v>
@@ -32523,7 +32703,7 @@
         <v>SLN1056</v>
       </c>
       <c r="C687" t="str">
-        <v>Sephia 前导线 30m LB-E21S</v>
+        <v>Sephia 前导线 30m LB-E21S | 2.5号</v>
       </c>
       <c r="D687" t="str">
         <v>透明色</v>
@@ -32567,7 +32747,7 @@
         <v>SLN1056</v>
       </c>
       <c r="C688" t="str">
-        <v>Sephia 前导线 30m LB-E21S</v>
+        <v>Sephia 前导线 30m LB-E21S | 3号</v>
       </c>
       <c r="D688" t="str">
         <v>透明色</v>
@@ -32655,7 +32835,7 @@
         <v>SLN1057</v>
       </c>
       <c r="C690" t="str">
-        <v>LIMITED PRO 前导线 悬停 NL-I33Q</v>
+        <v>LIMITED PRO 前导线 悬停 NL-I33Q | 2号</v>
       </c>
       <c r="D690" t="str">
         <v>黄绿色</v>
@@ -32699,7 +32879,7 @@
         <v>SLN1057</v>
       </c>
       <c r="C691" t="str">
-        <v>LIMITED PRO 前导线 悬停 NL-I33Q</v>
+        <v>LIMITED PRO 前导线 悬停 NL-I33Q | 2.5号</v>
       </c>
       <c r="D691" t="str">
         <v>黄绿色</v>
@@ -32743,7 +32923,7 @@
         <v>SLN1057</v>
       </c>
       <c r="C692" t="str">
-        <v>LIMITED PRO 前导线 悬停 NL-I33Q</v>
+        <v>LIMITED PRO 前导线 悬停 NL-I33Q | 3号</v>
       </c>
       <c r="D692" t="str">
         <v>黄绿色</v>
@@ -32831,7 +33011,7 @@
         <v>SLN1058</v>
       </c>
       <c r="C694" t="str">
-        <v>PITBULL 8 LP-M51W</v>
+        <v>PITBULL 8 LP-M51W | 0.8号</v>
       </c>
       <c r="D694" t="str">
         <v>黄绿色</v>
@@ -32875,7 +33055,7 @@
         <v>SLN1058</v>
       </c>
       <c r="C695" t="str">
-        <v>PITBULL 8 LP-M51W</v>
+        <v>PITBULL 8 LP-M51W | 1号</v>
       </c>
       <c r="D695" t="str">
         <v>黄绿色</v>
@@ -32919,7 +33099,7 @@
         <v>SLN1058</v>
       </c>
       <c r="C696" t="str">
-        <v>PITBULL 8 LP-M51W</v>
+        <v>PITBULL 8 LP-M51W | 1.2号</v>
       </c>
       <c r="D696" t="str">
         <v>黄绿色</v>
@@ -32963,7 +33143,7 @@
         <v>SLN1058</v>
       </c>
       <c r="C697" t="str">
-        <v>PITBULL 8 LP-M51W</v>
+        <v>PITBULL 8 LP-M51W | 1.5号</v>
       </c>
       <c r="D697" t="str">
         <v>黄绿色</v>
@@ -33007,7 +33187,7 @@
         <v>SLN1058</v>
       </c>
       <c r="C698" t="str">
-        <v>PITBULL 8 LP-M51W</v>
+        <v>PITBULL 8 LP-M51W | 2.0号</v>
       </c>
       <c r="D698" t="str">
         <v>黄绿色</v>
@@ -33095,7 +33275,7 @@
         <v>SLN1058</v>
       </c>
       <c r="C700" t="str">
-        <v>PITBULL 8 LP-M61W</v>
+        <v>PITBULL 8 LP-M61W | 0.8号</v>
       </c>
       <c r="D700" t="str">
         <v>黄绿色</v>
@@ -33139,7 +33319,7 @@
         <v>SLN1058</v>
       </c>
       <c r="C701" t="str">
-        <v>PITBULL 8 LP-M61W</v>
+        <v>PITBULL 8 LP-M61W | 1.0号</v>
       </c>
       <c r="D701" t="str">
         <v>黄绿色</v>
@@ -33183,7 +33363,7 @@
         <v>SLN1058</v>
       </c>
       <c r="C702" t="str">
-        <v>PITBULL 8 LP-M61W</v>
+        <v>PITBULL 8 LP-M61W | 1.2号</v>
       </c>
       <c r="D702" t="str">
         <v>黄绿色</v>
@@ -33227,7 +33407,7 @@
         <v>SLN1058</v>
       </c>
       <c r="C703" t="str">
-        <v>PITBULL 8 LP-M61W</v>
+        <v>PITBULL 8 LP-M61W | 1.5号</v>
       </c>
       <c r="D703" t="str">
         <v>黄绿色</v>
@@ -33271,7 +33451,7 @@
         <v>SLN1058</v>
       </c>
       <c r="C704" t="str">
-        <v>PITBULL 8 LP-M61W</v>
+        <v>PITBULL 8 LP-M61W | 2号</v>
       </c>
       <c r="D704" t="str">
         <v>黄绿色</v>

--- a/GearSage-client/pkgGear/data_raw/shimano_line_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_line_import.xlsx
@@ -458,7 +458,7 @@
         <v>PE</v>
       </c>
       <c r="H2" t="str">
-        <v>images/shimano_lines/Tanatoru 8_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%208_main.jpg</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -493,7 +493,7 @@
         <v>PE</v>
       </c>
       <c r="H3" t="str">
-        <v>images/shimano_lines/Tanatoru 4 _ 8 100m  连盘_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%204%20_%208%20100m%20%20%E8%BF%9E%E7%9B%98_main.jpg</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -528,7 +528,7 @@
         <v>PE</v>
       </c>
       <c r="H4" t="str">
-        <v>images/shimano_lines/PITBULL G9_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20G9_main.jpg</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -563,7 +563,7 @@
         <v>Nylon</v>
       </c>
       <c r="H5" t="str">
-        <v>images/shimano_lines/OCEA PLUGGER NYLON LEADER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20PLUGGER%20NYLON%20LEADER_main.jpg</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -598,7 +598,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H6" t="str">
-        <v>images/shimano_lines/PITBULL FLUORO LEADER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20FLUORO%20LEADER_main.jpg</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -633,7 +633,7 @@
         <v>PE</v>
       </c>
       <c r="H7" t="str">
-        <v>images/shimano_lines/OCEA 17+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%2017%2B_main.jpg</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -668,7 +668,7 @@
         <v>PE</v>
       </c>
       <c r="H8" t="str">
-        <v>images/shimano_lines/OCEA 8_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%208_main.jpg</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -703,7 +703,7 @@
         <v>PE</v>
       </c>
       <c r="H9" t="str">
-        <v>images/shimano_lines/OCEA JIGGER MX4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20JIGGER%20MX4_main.jpg</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -738,7 +738,7 @@
         <v>PE</v>
       </c>
       <c r="H10" t="str">
-        <v>images/shimano_lines/KISU SPECIAL EX4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20EX4%2013m_main.jpg</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -773,7 +773,7 @@
         <v>PE</v>
       </c>
       <c r="H11" t="str">
-        <v>images/shimano_lines/KISU SPECIAL G5_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20G5_main.jpg</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -808,7 +808,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H12" t="str">
-        <v>images/shimano_lines/OCEA EX 前导线_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20EX%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpg</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -843,7 +843,7 @@
         <v>PE</v>
       </c>
       <c r="H13" t="str">
-        <v>images/shimano_lines/LIMITED PRO G5+ PE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20G5%2B%20PE_main.jpg</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -878,7 +878,7 @@
         <v>PE</v>
       </c>
       <c r="H14" t="str">
-        <v>images/shimano_lines/PITBULL 12_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%2012_main.jpg</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -913,7 +913,7 @@
         <v>PE</v>
       </c>
       <c r="H15" t="str">
-        <v>images/shimano_lines/HARDBULL 8+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/HARDBULL%208%2B_main.jpg</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -948,7 +948,7 @@
         <v>PE</v>
       </c>
       <c r="H16" t="str">
-        <v>images/shimano_lines/GRAPPLER 8_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/GRAPPLER%208_main.jpg</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -983,7 +983,7 @@
         <v>PE</v>
       </c>
       <c r="H17" t="str">
-        <v>images/shimano_lines/KISU SPECIAL EX4 13m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20EX4%2013m_main.jpg</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1018,7 +1018,7 @@
         <v>PE</v>
       </c>
       <c r="H18" t="str">
-        <v>images/shimano_lines/Tanatoru 4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%204%20_%208%20100m%20%20%E8%BF%9E%E7%9B%98_main.jpg</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>Nylon</v>
       </c>
       <c r="H19" t="str">
-        <v>images/shimano_lines/KAIKON_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KAIKON_main.jpg</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1088,7 +1088,7 @@
         <v>Nylon</v>
       </c>
       <c r="H20" t="str">
-        <v>images/shimano_lines/BULL'S EYE 远投_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BULL'S%20EYE%20%E8%BF%9C%E6%8A%95_main.jpg</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H21" t="str">
-        <v>images/shimano_lines/OCEA JIGGER MASTER 前导线_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20JIGGER%20MASTER%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpg</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1158,7 +1158,7 @@
         <v>PE</v>
       </c>
       <c r="H22" t="str">
-        <v>images/shimano_lines/Sephia 8+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%208%2B_main.jpg</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1193,7 +1193,7 @@
         <v>PE</v>
       </c>
       <c r="H23" t="str">
-        <v>images/shimano_lines/PITBULL 8+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%208%2B_main.jpg</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1228,7 +1228,7 @@
         <v>Ester</v>
       </c>
       <c r="H24" t="str">
-        <v>images/shimano_lines/FUKASE 船_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FUKASE%20%E8%88%B9_main.jpg</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1263,7 +1263,7 @@
         <v>PE</v>
       </c>
       <c r="H25" t="str">
-        <v>images/shimano_lines/Sephia G5_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20G5_main.jpg</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1298,7 +1298,7 @@
         <v>PE</v>
       </c>
       <c r="H26" t="str">
-        <v>images/shimano_lines/Sephia 8_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%208%2B_main.jpg</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1333,7 +1333,7 @@
         <v>PE</v>
       </c>
       <c r="H27" t="str">
-        <v>images/shimano_lines/SPINPOWER EX4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/SPINPOWER%20EX4_main.jpg</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1368,7 +1368,7 @@
         <v>PE</v>
       </c>
       <c r="H28" t="str">
-        <v>images/shimano_lines/GRAPPLER 4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/GRAPPLER%204_main.jpg</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1403,7 +1403,7 @@
         <v>PE</v>
       </c>
       <c r="H29" t="str">
-        <v>images/shimano_lines/LAKEMASTER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LAKEMASTER_main.jpg</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1438,7 +1438,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H30" t="str">
-        <v>images/shimano_lines/LIMITED PRO MASTER TOUGH-MUD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20MASTER%20TOUGH-MUD_main.jpg</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1473,7 +1473,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H31" t="str">
-        <v>images/shimano_lines/LIMITED PRO MASTER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20MASTER%20TOUGH-MUD_main.jpg</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1508,7 +1508,7 @@
         <v>Nylon</v>
       </c>
       <c r="H32" t="str">
-        <v>images/shimano_lines/BB-X HYPER-REPEL α 漂浮_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20HYPER-REPEL%20%CE%B1%20%E6%BC%82%E6%B5%AE_main.jpg</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1543,7 +1543,7 @@
         <v>Nylon</v>
       </c>
       <c r="H33" t="str">
-        <v>images/shimano_lines/BB-X PLASMA WHITE FLOAT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20PLASMA%20WHITE%20FLOAT_main.jpg</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1578,7 +1578,7 @@
         <v>PE</v>
       </c>
       <c r="H34" t="str">
-        <v>images/shimano_lines/PITBULL 4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%204%2B_main.jpg</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1613,7 +1613,7 @@
         <v>Nylon</v>
       </c>
       <c r="H35" t="str">
-        <v>images/shimano_lines/LIMITED PRO HYPER-REPEL α ZERO 漂浮_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%BC%82%E6%B5%AE_main.jpg</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1648,7 +1648,7 @@
         <v>Nylon</v>
       </c>
       <c r="H36" t="str">
-        <v>images/shimano_lines/LIMITED PRO 矶 ZERO 悬停 150m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20%E7%9F%B6%20ZERO%20%E6%82%AC%E5%81%9C%20150m_main.jpg</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1683,7 +1683,7 @@
         <v>Nylon</v>
       </c>
       <c r="H37" t="str">
-        <v>images/shimano_lines/BB-X PLASMA WHITE ZERO SUSPEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20PLASMA%20WHITE%20ZERO%20SUSPEND_main.jpg</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1718,7 +1718,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H38" t="str">
-        <v>images/shimano_lines/MASTIFF FC 90m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/MASTIFF%20FC%2090m_main.jpg</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1753,7 +1753,7 @@
         <v>Nylon</v>
       </c>
       <c r="H39" t="str">
-        <v>images/shimano_lines/OCEA 前导线_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpg</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1788,7 +1788,7 @@
         <v>Nylon</v>
       </c>
       <c r="H40" t="str">
-        <v>images/shimano_lines/FIREBLOOD HYPER-REPEL α ZERO 漂浮_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%BC%82%E6%B5%AE_main.jpg</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1823,7 +1823,7 @@
         <v>Nylon</v>
       </c>
       <c r="H41" t="str">
-        <v>images/shimano_lines/FIREBLOOD HYPER-REPEL α ZERO 悬停_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%82%AC%E5%81%9C_main.jpg</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1858,7 +1858,7 @@
         <v>Nylon</v>
       </c>
       <c r="H42" t="str">
-        <v>images/shimano_lines/BB-X HYPER-REPEL α 悬停_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20HYPER-REPEL%20%CE%B1%20%E6%82%AC%E5%81%9C_main.jpg</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1893,7 +1893,7 @@
         <v>PE</v>
       </c>
       <c r="H43" t="str">
-        <v>images/shimano_lines/OCEA 16 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%2016%2030m_main.jpg</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1928,7 +1928,7 @@
         <v>PE</v>
       </c>
       <c r="H44" t="str">
-        <v>images/shimano_lines/PITBULL 4+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%204%2B_main.jpg</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1963,7 +1963,7 @@
         <v>PE</v>
       </c>
       <c r="H45" t="str">
-        <v>images/shimano_lines/BASIS G5 PE SUSPEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BASIS%20G5%20PE%20SUSPEND_main.jpg</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1998,7 +1998,7 @@
         <v>Nylon</v>
       </c>
       <c r="H46" t="str">
-        <v>images/shimano_lines/FIREBLOOD STRETCH 悬停_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20STRETCH%20%E6%82%AC%E5%81%9C_main.jpg</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2033,7 +2033,7 @@
         <v>Ester</v>
       </c>
       <c r="H47" t="str">
-        <v>images/shimano_lines/SIGHT LASER EX 240m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/SIGHT%20LASER%20EX%20240m_main.jpg</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2068,7 +2068,7 @@
         <v>PE</v>
       </c>
       <c r="H48" t="str">
-        <v>images/shimano_lines/PITBULL G5_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20G5_main.jpg</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2103,7 +2103,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H49" t="str">
-        <v>images/shimano_lines/Soare AJING 150m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Soare%20AJING%20150m_main.jpg</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2138,7 +2138,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H50" t="str">
-        <v>images/shimano_lines/Sephia MASTER 前导线 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20MASTER%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpg</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2173,7 +2173,7 @@
         <v>PE</v>
       </c>
       <c r="H51" t="str">
-        <v>images/shimano_lines/BB BRAID_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB%20BRAID_main.jpg</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2208,7 +2208,7 @@
         <v>Nylon</v>
       </c>
       <c r="H52" t="str">
-        <v>images/shimano_lines/BAISIS 矶_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BAISIS%20%E7%9F%B6_main.jpg</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2243,7 +2243,7 @@
         <v>Nylon</v>
       </c>
       <c r="H53" t="str">
-        <v>images/shimano_lines/BASIS ORANGE ZERO SUSPEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BASIS%20ORANGE%20ZERO%20SUSPEND_main.jpg</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2278,7 +2278,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H54" t="str">
-        <v>images/shimano_lines/BAISIS EX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BAISIS%20EX_main.jpg</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2313,7 +2313,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H55" t="str">
-        <v>images/shimano_lines/EXSENCE 前导线 EX 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/EXSENCE%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20EX%2030m_main.jpg</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2348,7 +2348,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H56" t="str">
-        <v>images/shimano_lines/炎月 EX 前导线 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/%E7%82%8E%E6%9C%88%20EX%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpg</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H57" t="str">
-        <v>images/shimano_lines/Soare 前导线 EX 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Soare%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20EX%2030m_main.jpg</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2418,7 +2418,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H58" t="str">
-        <v>images/shimano_lines/Sephia 前导线 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpg</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Nylon</v>
       </c>
       <c r="H59" t="str">
-        <v>images/shimano_lines/LIMITED PRO 前导线 悬停_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20%E6%82%AC%E5%81%9C_main.jpg</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2488,7 +2488,7 @@
         <v>PE</v>
       </c>
       <c r="H60" t="str">
-        <v>images/shimano_lines/PITBULL 8_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%208%2B_main.jpg</v>
       </c>
       <c r="I60" t="str">
         <v/>
